--- a/data.mn/public/datasets/weekly-vegetable-prices-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/weekly-vegetable-prices-ulaanbaatar.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7638,6 +7638,206 @@
         <v>2072</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3571</v>
+      </c>
+      <c r="D289" t="n">
+        <v>2950</v>
+      </c>
+      <c r="E289" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3954</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3466</v>
+      </c>
+      <c r="D290" t="n">
+        <v>2876</v>
+      </c>
+      <c r="E290" t="n">
+        <v>3552</v>
+      </c>
+      <c r="F290" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2876</v>
+      </c>
+      <c r="E291" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F291" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D292" t="n">
+        <v>2855</v>
+      </c>
+      <c r="E292" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F292" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2855</v>
+      </c>
+      <c r="E293" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F293" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C294" t="n">
+        <v>3015</v>
+      </c>
+      <c r="D294" t="n">
+        <v>2759</v>
+      </c>
+      <c r="E294" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F294" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G294" t="n">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C295" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2759</v>
+      </c>
+      <c r="E295" t="n">
+        <v>3515</v>
+      </c>
+      <c r="F295" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G295" t="n">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D296" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E296" t="n">
+        <v>3618</v>
+      </c>
+      <c r="F296" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G296" t="n">
+        <v>2274</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7649,16 +7849,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7674,27 +7874,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Хүрэн манжин, кг</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Байцаа, кг</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Лууван, кг</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Сонгино, кг</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Төмс, кг</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Хүрэн манжин, кг</t>
         </is>
       </c>
     </row>
@@ -7708,19 +7908,19 @@
         <v>4985</v>
       </c>
       <c r="C2" t="n">
+        <v>2315</v>
+      </c>
+      <c r="D2" t="n">
         <v>1719</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1550</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1691</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>935</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2315</v>
       </c>
     </row>
     <row r="3">
@@ -7733,19 +7933,19 @@
         <v>4985</v>
       </c>
       <c r="C3" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D3" t="n">
         <v>1725</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1550</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1691</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>935</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2343</v>
       </c>
     </row>
     <row r="4">
@@ -7758,19 +7958,19 @@
         <v>5026</v>
       </c>
       <c r="C4" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D4" t="n">
         <v>1750</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1562</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1691</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>935</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2343</v>
       </c>
     </row>
     <row r="5">
@@ -7783,19 +7983,19 @@
         <v>5026</v>
       </c>
       <c r="C5" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D5" t="n">
         <v>1827</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1562</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1691</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>985</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2343</v>
       </c>
     </row>
     <row r="6">
@@ -7808,19 +8008,19 @@
         <v>5026</v>
       </c>
       <c r="C6" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D6" t="n">
         <v>1816</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>1536</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1715</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>968</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2343</v>
       </c>
     </row>
     <row r="7">
@@ -7833,19 +8033,19 @@
         <v>5026</v>
       </c>
       <c r="C7" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D7" t="n">
         <v>1816</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1536</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1715</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>968</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2343</v>
       </c>
     </row>
     <row r="8">
@@ -7858,19 +8058,19 @@
         <v>5026</v>
       </c>
       <c r="C8" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D8" t="n">
         <v>1851</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>1558</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1801</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>968</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2343</v>
       </c>
     </row>
     <row r="9">
@@ -7883,19 +8083,19 @@
         <v>5026</v>
       </c>
       <c r="C9" t="n">
+        <v>2376</v>
+      </c>
+      <c r="D9" t="n">
         <v>1903</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>1558</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1801</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>968</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2376</v>
       </c>
     </row>
     <row r="10">
@@ -7908,19 +8108,19 @@
         <v>5026</v>
       </c>
       <c r="C10" t="n">
+        <v>2418</v>
+      </c>
+      <c r="D10" t="n">
         <v>1903</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>1558</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1878</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>968</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2418</v>
       </c>
     </row>
     <row r="11">
@@ -7933,19 +8133,19 @@
         <v>5026</v>
       </c>
       <c r="C11" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D11" t="n">
         <v>1932</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>1550</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1878</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>968</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2501</v>
       </c>
     </row>
     <row r="12">
@@ -7958,19 +8158,19 @@
         <v>5026</v>
       </c>
       <c r="C12" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D12" t="n">
         <v>1932</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>1550</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1878</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>968</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2501</v>
       </c>
     </row>
     <row r="13">
@@ -7983,19 +8183,19 @@
         <v>5059</v>
       </c>
       <c r="C13" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D13" t="n">
         <v>1932</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1550</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1878</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>968</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2501</v>
       </c>
     </row>
     <row r="14">
@@ -8008,19 +8208,19 @@
         <v>5059</v>
       </c>
       <c r="C14" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D14" t="n">
         <v>1932</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1550</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1878</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>968</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2501</v>
       </c>
     </row>
     <row r="15">
@@ -8033,19 +8233,19 @@
         <v>5112</v>
       </c>
       <c r="C15" t="n">
+        <v>2572</v>
+      </c>
+      <c r="D15" t="n">
         <v>2026</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>1550</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1878</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>968</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2572</v>
       </c>
     </row>
     <row r="16">
@@ -8058,19 +8258,19 @@
         <v>5206</v>
       </c>
       <c r="C16" t="n">
+        <v>2667</v>
+      </c>
+      <c r="D16" t="n">
         <v>2130</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>1550</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>2011</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>968</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2667</v>
       </c>
     </row>
     <row r="17">
@@ -8083,19 +8283,19 @@
         <v>5206</v>
       </c>
       <c r="C17" t="n">
+        <v>2706</v>
+      </c>
+      <c r="D17" t="n">
         <v>2151</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>1550</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>2069</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>954</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2706</v>
       </c>
     </row>
     <row r="18">
@@ -8108,19 +8308,19 @@
         <v>5206</v>
       </c>
       <c r="C18" t="n">
+        <v>2751</v>
+      </c>
+      <c r="D18" t="n">
         <v>2259</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>1584</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>2069</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>954</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2751</v>
       </c>
     </row>
     <row r="19">
@@ -8133,19 +8333,19 @@
         <v>5206</v>
       </c>
       <c r="C19" t="n">
+        <v>2751</v>
+      </c>
+      <c r="D19" t="n">
         <v>2376</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1593</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>2069</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>968</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2751</v>
       </c>
     </row>
     <row r="20">
@@ -8158,19 +8358,19 @@
         <v>5422</v>
       </c>
       <c r="C20" t="n">
+        <v>2792</v>
+      </c>
+      <c r="D20" t="n">
         <v>2413</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>1610</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>2049</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>968</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2792</v>
       </c>
     </row>
     <row r="21">
@@ -8183,19 +8383,19 @@
         <v>5580</v>
       </c>
       <c r="C21" t="n">
+        <v>2792</v>
+      </c>
+      <c r="D21" t="n">
         <v>2564</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>1639</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>2049</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>968</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2792</v>
       </c>
     </row>
     <row r="22">
@@ -8208,19 +8408,19 @@
         <v>5580</v>
       </c>
       <c r="C22" t="n">
+        <v>2792</v>
+      </c>
+      <c r="D22" t="n">
         <v>2582</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>1639</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2125</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>960</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2792</v>
       </c>
     </row>
     <row r="23">
@@ -8233,19 +8433,19 @@
         <v>5580</v>
       </c>
       <c r="C23" t="n">
+        <v>2792</v>
+      </c>
+      <c r="D23" t="n">
         <v>2633</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>1688</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>2125</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>960</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2792</v>
       </c>
     </row>
     <row r="24">
@@ -8258,19 +8458,19 @@
         <v>5580</v>
       </c>
       <c r="C24" t="n">
+        <v>2952</v>
+      </c>
+      <c r="D24" t="n">
         <v>2605</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>1688</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>2147</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>960</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2952</v>
       </c>
     </row>
     <row r="25">
@@ -8283,19 +8483,19 @@
         <v>5580</v>
       </c>
       <c r="C25" t="n">
+        <v>2905</v>
+      </c>
+      <c r="D25" t="n">
         <v>2584</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>1688</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>2147</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>960</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2905</v>
       </c>
     </row>
     <row r="26">
@@ -8308,19 +8508,19 @@
         <v>5656</v>
       </c>
       <c r="C26" t="n">
+        <v>3222</v>
+      </c>
+      <c r="D26" t="n">
         <v>2791</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>1892</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>2147</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>960</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3222</v>
       </c>
     </row>
     <row r="27">
@@ -8333,19 +8533,19 @@
         <v>5843</v>
       </c>
       <c r="C27" t="n">
+        <v>3222</v>
+      </c>
+      <c r="D27" t="n">
         <v>2965</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>1997</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>2147</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>960</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3222</v>
       </c>
     </row>
     <row r="28">
@@ -8358,19 +8558,19 @@
         <v>5737</v>
       </c>
       <c r="C28" t="n">
+        <v>3222</v>
+      </c>
+      <c r="D28" t="n">
         <v>3129</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>2051</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>2749</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>973</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3222</v>
       </c>
     </row>
     <row r="29">
@@ -8383,19 +8583,19 @@
         <v>5737</v>
       </c>
       <c r="C29" t="n">
+        <v>3222</v>
+      </c>
+      <c r="D29" t="n">
         <v>3168</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>2121</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>2757</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>973</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3222</v>
       </c>
     </row>
     <row r="30">
@@ -8408,19 +8608,19 @@
         <v>5934</v>
       </c>
       <c r="C30" t="n">
+        <v>3230</v>
+      </c>
+      <c r="D30" t="n">
         <v>2925</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>2444</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>2807</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>954</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3230</v>
       </c>
     </row>
     <row r="31">
@@ -8433,19 +8633,19 @@
         <v>5985</v>
       </c>
       <c r="C31" t="n">
+        <v>3230</v>
+      </c>
+      <c r="D31" t="n">
         <v>2925</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>2487</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>2807</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>944</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3230</v>
       </c>
     </row>
     <row r="32">
@@ -8458,19 +8658,19 @@
         <v>5985</v>
       </c>
       <c r="C32" t="n">
+        <v>3194</v>
+      </c>
+      <c r="D32" t="n">
         <v>2795</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>2858</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>2807</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>987</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3194</v>
       </c>
     </row>
     <row r="33">
@@ -8483,19 +8683,19 @@
         <v>5985</v>
       </c>
       <c r="C33" t="n">
+        <v>3169</v>
+      </c>
+      <c r="D33" t="n">
         <v>2575</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>2953</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>2807</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>963</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3169</v>
       </c>
     </row>
     <row r="34">
@@ -8508,19 +8708,19 @@
         <v>6063</v>
       </c>
       <c r="C34" t="n">
+        <v>3107</v>
+      </c>
+      <c r="D34" t="n">
         <v>2220</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>3093</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>2807</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>956</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3107</v>
       </c>
     </row>
     <row r="35">
@@ -8533,19 +8733,19 @@
         <v>5810</v>
       </c>
       <c r="C35" t="n">
+        <v>2989</v>
+      </c>
+      <c r="D35" t="n">
         <v>1808</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>3030</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>2781</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>930</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2989</v>
       </c>
     </row>
     <row r="36">
@@ -8558,19 +8758,19 @@
         <v>5810</v>
       </c>
       <c r="C36" t="n">
+        <v>2922</v>
+      </c>
+      <c r="D36" t="n">
         <v>1766</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>2467</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>2781</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>917</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2922</v>
       </c>
     </row>
     <row r="37">
@@ -8583,19 +8783,19 @@
         <v>5759</v>
       </c>
       <c r="C37" t="n">
+        <v>2922</v>
+      </c>
+      <c r="D37" t="n">
         <v>1692</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>2348</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>2781</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>869</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2922</v>
       </c>
     </row>
     <row r="38">
@@ -8608,19 +8808,19 @@
         <v>5759</v>
       </c>
       <c r="C38" t="n">
+        <v>2749</v>
+      </c>
+      <c r="D38" t="n">
         <v>1692</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>2321</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>2508</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>859</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2749</v>
       </c>
     </row>
     <row r="39">
@@ -8633,19 +8833,19 @@
         <v>5759</v>
       </c>
       <c r="C39" t="n">
+        <v>2749</v>
+      </c>
+      <c r="D39" t="n">
         <v>1654</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>2198</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>2508</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>813</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2749</v>
       </c>
     </row>
     <row r="40">
@@ -8658,19 +8858,19 @@
         <v>5759</v>
       </c>
       <c r="C40" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D40" t="n">
         <v>1654</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>2198</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>2553</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>813</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2778</v>
       </c>
     </row>
     <row r="41">
@@ -8683,19 +8883,19 @@
         <v>5805</v>
       </c>
       <c r="C41" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D41" t="n">
         <v>1685</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>2263</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>2552</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>772</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2729</v>
       </c>
     </row>
     <row r="42">
@@ -8708,19 +8908,19 @@
         <v>5805</v>
       </c>
       <c r="C42" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D42" t="n">
         <v>1737</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>2280</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>2552</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>788</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2729</v>
       </c>
     </row>
     <row r="43">
@@ -8733,19 +8933,19 @@
         <v>5805</v>
       </c>
       <c r="C43" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D43" t="n">
         <v>1910</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>2367</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>2552</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>840</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3006</v>
       </c>
     </row>
     <row r="44">
@@ -8758,19 +8958,19 @@
         <v>6118</v>
       </c>
       <c r="C44" t="n">
+        <v>3118</v>
+      </c>
+      <c r="D44" t="n">
         <v>1966</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>2518</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>2658</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>893</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3118</v>
       </c>
     </row>
     <row r="45">
@@ -8783,19 +8983,19 @@
         <v>6879</v>
       </c>
       <c r="C45" t="n">
+        <v>3279</v>
+      </c>
+      <c r="D45" t="n">
         <v>2006</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>2598</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>2669</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>946</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3279</v>
       </c>
     </row>
     <row r="46">
@@ -8808,19 +9008,19 @@
         <v>7061</v>
       </c>
       <c r="C46" t="n">
+        <v>3424</v>
+      </c>
+      <c r="D46" t="n">
         <v>2024</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>2553</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>2669</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>1006</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3424</v>
       </c>
     </row>
     <row r="47">
@@ -8833,19 +9033,19 @@
         <v>8179</v>
       </c>
       <c r="C47" t="n">
+        <v>3424</v>
+      </c>
+      <c r="D47" t="n">
         <v>2192</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>2729</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>2669</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>1061</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3424</v>
       </c>
     </row>
     <row r="48">
@@ -8858,19 +9058,19 @@
         <v>8225</v>
       </c>
       <c r="C48" t="n">
+        <v>3733</v>
+      </c>
+      <c r="D48" t="n">
         <v>2356</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>2855</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>2687</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>1070</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3733</v>
       </c>
     </row>
     <row r="49">
@@ -8883,19 +9083,19 @@
         <v>8225</v>
       </c>
       <c r="C49" t="n">
+        <v>3733</v>
+      </c>
+      <c r="D49" t="n">
         <v>2326</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>2815</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>2687</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>1098</v>
-      </c>
-      <c r="G49" t="n">
-        <v>3733</v>
       </c>
     </row>
     <row r="50">
@@ -8908,19 +9108,19 @@
         <v>8041</v>
       </c>
       <c r="C50" t="n">
+        <v>3738</v>
+      </c>
+      <c r="D50" t="n">
         <v>2340</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>2868</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>2819</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>1091</v>
-      </c>
-      <c r="G50" t="n">
-        <v>3738</v>
       </c>
     </row>
     <row r="51">
@@ -8933,19 +9133,19 @@
         <v>7851</v>
       </c>
       <c r="C51" t="n">
+        <v>3620</v>
+      </c>
+      <c r="D51" t="n">
         <v>2437</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>2981</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>2696</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>1183</v>
-      </c>
-      <c r="G51" t="n">
-        <v>3620</v>
       </c>
     </row>
     <row r="52">
@@ -8958,19 +9158,19 @@
         <v>7851</v>
       </c>
       <c r="C52" t="n">
+        <v>3719</v>
+      </c>
+      <c r="D52" t="n">
         <v>2361</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>3034</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>2687</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>1152</v>
-      </c>
-      <c r="G52" t="n">
-        <v>3719</v>
       </c>
     </row>
     <row r="53">
@@ -8983,19 +9183,19 @@
         <v>7851</v>
       </c>
       <c r="C53" t="n">
+        <v>3631</v>
+      </c>
+      <c r="D53" t="n">
         <v>2377</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>3027</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>2687</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>1132</v>
-      </c>
-      <c r="G53" t="n">
-        <v>3631</v>
       </c>
     </row>
     <row r="54">
@@ -9008,19 +9208,19 @@
         <v>7851</v>
       </c>
       <c r="C54" t="n">
+        <v>3804</v>
+      </c>
+      <c r="D54" t="n">
         <v>2446</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>3098</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>2687</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>1147</v>
-      </c>
-      <c r="G54" t="n">
-        <v>3804</v>
       </c>
     </row>
     <row r="55">
@@ -9033,19 +9233,19 @@
         <v>7851</v>
       </c>
       <c r="C55" t="n">
+        <v>3804</v>
+      </c>
+      <c r="D55" t="n">
         <v>2473</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>3135</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>2687</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>1204</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3804</v>
       </c>
     </row>
     <row r="56">
@@ -9058,19 +9258,19 @@
         <v>7851</v>
       </c>
       <c r="C56" t="n">
+        <v>3791</v>
+      </c>
+      <c r="D56" t="n">
         <v>2430</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>3135</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>2687</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>1171</v>
-      </c>
-      <c r="G56" t="n">
-        <v>3791</v>
       </c>
     </row>
     <row r="57">
@@ -9083,19 +9283,19 @@
         <v>7851</v>
       </c>
       <c r="C57" t="n">
+        <v>3786</v>
+      </c>
+      <c r="D57" t="n">
         <v>2430</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>3135</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>2687</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>1210</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3786</v>
       </c>
     </row>
     <row r="58">
@@ -9108,19 +9308,19 @@
         <v>7851</v>
       </c>
       <c r="C58" t="n">
+        <v>3835</v>
+      </c>
+      <c r="D58" t="n">
         <v>2552</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>3067</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>2687</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>1191</v>
-      </c>
-      <c r="G58" t="n">
-        <v>3835</v>
       </c>
     </row>
     <row r="59">
@@ -9133,19 +9333,19 @@
         <v>7851</v>
       </c>
       <c r="C59" t="n">
+        <v>3613</v>
+      </c>
+      <c r="D59" t="n">
         <v>2479</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>3047</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>2687</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>1139</v>
-      </c>
-      <c r="G59" t="n">
-        <v>3613</v>
       </c>
     </row>
     <row r="60">
@@ -9158,19 +9358,19 @@
         <v>7851</v>
       </c>
       <c r="C60" t="n">
+        <v>3574</v>
+      </c>
+      <c r="D60" t="n">
         <v>2488</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>2995</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>2687</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>1139</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3574</v>
       </c>
     </row>
     <row r="61">
@@ -9183,19 +9383,19 @@
         <v>7851</v>
       </c>
       <c r="C61" t="n">
+        <v>3657</v>
+      </c>
+      <c r="D61" t="n">
         <v>2523</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>2995</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>2687</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>1172</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3657</v>
       </c>
     </row>
     <row r="62">
@@ -9208,19 +9408,19 @@
         <v>7851</v>
       </c>
       <c r="C62" t="n">
+        <v>3754</v>
+      </c>
+      <c r="D62" t="n">
         <v>2672</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>3074</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>2687</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>1179</v>
-      </c>
-      <c r="G62" t="n">
-        <v>3754</v>
       </c>
     </row>
     <row r="63">
@@ -9233,19 +9433,19 @@
         <v>7851</v>
       </c>
       <c r="C63" t="n">
+        <v>3652</v>
+      </c>
+      <c r="D63" t="n">
         <v>2703</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>3031</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>2687</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>1179</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3652</v>
       </c>
     </row>
     <row r="64">
@@ -9258,19 +9458,19 @@
         <v>7851</v>
       </c>
       <c r="C64" t="n">
+        <v>3714</v>
+      </c>
+      <c r="D64" t="n">
         <v>2742</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>3074</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>2687</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>1244</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3714</v>
       </c>
     </row>
     <row r="65">
@@ -9283,19 +9483,19 @@
         <v>7851</v>
       </c>
       <c r="C65" t="n">
+        <v>3759</v>
+      </c>
+      <c r="D65" t="n">
         <v>2768</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>3074</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>2687</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>1347</v>
-      </c>
-      <c r="G65" t="n">
-        <v>3759</v>
       </c>
     </row>
     <row r="66">
@@ -9308,19 +9508,19 @@
         <v>7851</v>
       </c>
       <c r="C66" t="n">
+        <v>3912</v>
+      </c>
+      <c r="D66" t="n">
         <v>2997</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
         <v>3246</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>2687</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>1381</v>
-      </c>
-      <c r="G66" t="n">
-        <v>3912</v>
       </c>
     </row>
     <row r="67">
@@ -9333,19 +9533,19 @@
         <v>7851</v>
       </c>
       <c r="C67" t="n">
+        <v>4002</v>
+      </c>
+      <c r="D67" t="n">
         <v>3172</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
         <v>3192</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>2726</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>1435</v>
-      </c>
-      <c r="G67" t="n">
-        <v>4002</v>
       </c>
     </row>
     <row r="68">
@@ -9358,19 +9558,19 @@
         <v>7851</v>
       </c>
       <c r="C68" t="n">
+        <v>4002</v>
+      </c>
+      <c r="D68" t="n">
         <v>3309</v>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
         <v>3268</v>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>2726</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>1435</v>
-      </c>
-      <c r="G68" t="n">
-        <v>4002</v>
       </c>
     </row>
     <row r="69">
@@ -9383,19 +9583,19 @@
         <v>7851</v>
       </c>
       <c r="C69" t="n">
+        <v>5032</v>
+      </c>
+      <c r="D69" t="n">
         <v>3362</v>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
         <v>3465</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>2787</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>1463</v>
-      </c>
-      <c r="G69" t="n">
-        <v>5032</v>
       </c>
     </row>
     <row r="70">
@@ -9408,19 +9608,19 @@
         <v>8041</v>
       </c>
       <c r="C70" t="n">
+        <v>5769</v>
+      </c>
+      <c r="D70" t="n">
         <v>3581</v>
       </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
         <v>3807</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>2787</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>1530</v>
-      </c>
-      <c r="G70" t="n">
-        <v>5769</v>
       </c>
     </row>
     <row r="71">
@@ -9433,19 +9633,19 @@
         <v>8041</v>
       </c>
       <c r="C71" t="n">
+        <v>5734</v>
+      </c>
+      <c r="D71" t="n">
         <v>3534</v>
       </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
         <v>3714</v>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>2787</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>1530</v>
-      </c>
-      <c r="G71" t="n">
-        <v>5734</v>
       </c>
     </row>
     <row r="72">
@@ -9458,19 +9658,19 @@
         <v>8041</v>
       </c>
       <c r="C72" t="n">
+        <v>5734</v>
+      </c>
+      <c r="D72" t="n">
         <v>3608</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
         <v>3821</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>2787</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>1542</v>
-      </c>
-      <c r="G72" t="n">
-        <v>5734</v>
       </c>
     </row>
     <row r="73">
@@ -9483,19 +9683,19 @@
         <v>8041</v>
       </c>
       <c r="C73" t="n">
+        <v>5734</v>
+      </c>
+      <c r="D73" t="n">
         <v>3608</v>
       </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
         <v>3971</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>2787</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>1542</v>
-      </c>
-      <c r="G73" t="n">
-        <v>5734</v>
       </c>
     </row>
     <row r="74">
@@ -9508,19 +9708,19 @@
         <v>8041</v>
       </c>
       <c r="C74" t="n">
+        <v>5616</v>
+      </c>
+      <c r="D74" t="n">
         <v>3940</v>
       </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
         <v>4171</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>2787</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>1609</v>
-      </c>
-      <c r="G74" t="n">
-        <v>5616</v>
       </c>
     </row>
     <row r="75">
@@ -9533,19 +9733,19 @@
         <v>8041</v>
       </c>
       <c r="C75" t="n">
+        <v>5846</v>
+      </c>
+      <c r="D75" t="n">
         <v>4532</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>4225</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>2787</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>1891</v>
-      </c>
-      <c r="G75" t="n">
-        <v>5846</v>
       </c>
     </row>
     <row r="76">
@@ -9558,19 +9758,19 @@
         <v>8041</v>
       </c>
       <c r="C76" t="n">
+        <v>5906</v>
+      </c>
+      <c r="D76" t="n">
         <v>4942</v>
       </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
         <v>4536</v>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>2787</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>2334</v>
-      </c>
-      <c r="G76" t="n">
-        <v>5906</v>
       </c>
     </row>
     <row r="77">
@@ -9583,19 +9783,19 @@
         <v>8041</v>
       </c>
       <c r="C77" t="n">
+        <v>5666</v>
+      </c>
+      <c r="D77" t="n">
         <v>5092</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>4724</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>2787</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>2511</v>
-      </c>
-      <c r="G77" t="n">
-        <v>5666</v>
       </c>
     </row>
     <row r="78">
@@ -9608,19 +9808,19 @@
         <v>8041</v>
       </c>
       <c r="C78" t="n">
+        <v>5624</v>
+      </c>
+      <c r="D78" t="n">
         <v>5011</v>
       </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
         <v>4779</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>2787</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>2490</v>
-      </c>
-      <c r="G78" t="n">
-        <v>5624</v>
       </c>
     </row>
     <row r="79">
@@ -9633,19 +9833,19 @@
         <v>8041</v>
       </c>
       <c r="C79" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D79" t="n">
         <v>4641</v>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>4706</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>3967</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>2550</v>
-      </c>
-      <c r="G79" t="n">
-        <v>5560</v>
       </c>
     </row>
     <row r="80">
@@ -9658,19 +9858,19 @@
         <v>7176</v>
       </c>
       <c r="C80" t="n">
+        <v>5341</v>
+      </c>
+      <c r="D80" t="n">
         <v>3529</v>
       </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
         <v>4465</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>4298</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>3591</v>
-      </c>
-      <c r="G80" t="n">
-        <v>5341</v>
       </c>
     </row>
     <row r="81">
@@ -9683,19 +9883,19 @@
         <v>6772</v>
       </c>
       <c r="C81" t="n">
+        <v>5368</v>
+      </c>
+      <c r="D81" t="n">
         <v>2930</v>
       </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
         <v>4742</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>4499</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>4077</v>
-      </c>
-      <c r="G81" t="n">
-        <v>5368</v>
       </c>
     </row>
     <row r="82">
@@ -9708,19 +9908,19 @@
         <v>6772</v>
       </c>
       <c r="C82" t="n">
+        <v>4931</v>
+      </c>
+      <c r="D82" t="n">
         <v>2416</v>
       </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
         <v>4440</v>
       </c>
-      <c r="E82" t="n">
+      <c r="F82" t="n">
         <v>4336</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>2715</v>
-      </c>
-      <c r="G82" t="n">
-        <v>4931</v>
       </c>
     </row>
     <row r="83">
@@ -9733,19 +9933,19 @@
         <v>6443</v>
       </c>
       <c r="C83" t="n">
+        <v>4471</v>
+      </c>
+      <c r="D83" t="n">
         <v>2215</v>
       </c>
-      <c r="D83" t="n">
+      <c r="E83" t="n">
         <v>3998</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>3770</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>2254</v>
-      </c>
-      <c r="G83" t="n">
-        <v>4471</v>
       </c>
     </row>
     <row r="84">
@@ -9758,19 +9958,19 @@
         <v>6443</v>
       </c>
       <c r="C84" t="n">
+        <v>4199</v>
+      </c>
+      <c r="D84" t="n">
         <v>1844</v>
       </c>
-      <c r="D84" t="n">
+      <c r="E84" t="n">
         <v>3474</v>
       </c>
-      <c r="E84" t="n">
+      <c r="F84" t="n">
         <v>3427</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>1650</v>
-      </c>
-      <c r="G84" t="n">
-        <v>4199</v>
       </c>
     </row>
     <row r="85">
@@ -9783,19 +9983,19 @@
         <v>6443</v>
       </c>
       <c r="C85" t="n">
+        <v>3961</v>
+      </c>
+      <c r="D85" t="n">
         <v>1890</v>
       </c>
-      <c r="D85" t="n">
+      <c r="E85" t="n">
         <v>2890</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>3062</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>1499</v>
-      </c>
-      <c r="G85" t="n">
-        <v>3961</v>
       </c>
     </row>
     <row r="86">
@@ -9808,19 +10008,19 @@
         <v>6443</v>
       </c>
       <c r="C86" t="n">
+        <v>3368</v>
+      </c>
+      <c r="D86" t="n">
         <v>1805</v>
       </c>
-      <c r="D86" t="n">
+      <c r="E86" t="n">
         <v>2629</v>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>2784</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>1409</v>
-      </c>
-      <c r="G86" t="n">
-        <v>3368</v>
       </c>
     </row>
     <row r="87">
@@ -9833,19 +10033,19 @@
         <v>6512</v>
       </c>
       <c r="C87" t="n">
+        <v>3446</v>
+      </c>
+      <c r="D87" t="n">
         <v>1919</v>
       </c>
-      <c r="D87" t="n">
+      <c r="E87" t="n">
         <v>2598</v>
       </c>
-      <c r="E87" t="n">
+      <c r="F87" t="n">
         <v>2634</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>1371</v>
-      </c>
-      <c r="G87" t="n">
-        <v>3446</v>
       </c>
     </row>
     <row r="88">
@@ -9858,19 +10058,19 @@
         <v>6763</v>
       </c>
       <c r="C88" t="n">
+        <v>3164</v>
+      </c>
+      <c r="D88" t="n">
         <v>1853</v>
       </c>
-      <c r="D88" t="n">
+      <c r="E88" t="n">
         <v>2312</v>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>2615</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>1330</v>
-      </c>
-      <c r="G88" t="n">
-        <v>3164</v>
       </c>
     </row>
     <row r="89">
@@ -9883,19 +10083,19 @@
         <v>6763</v>
       </c>
       <c r="C89" t="n">
+        <v>2985</v>
+      </c>
+      <c r="D89" t="n">
         <v>1766</v>
       </c>
-      <c r="D89" t="n">
+      <c r="E89" t="n">
         <v>2158</v>
       </c>
-      <c r="E89" t="n">
+      <c r="F89" t="n">
         <v>2615</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>1262</v>
-      </c>
-      <c r="G89" t="n">
-        <v>2985</v>
       </c>
     </row>
     <row r="90">
@@ -9908,19 +10108,19 @@
         <v>6763</v>
       </c>
       <c r="C90" t="n">
+        <v>2641</v>
+      </c>
+      <c r="D90" t="n">
         <v>1742</v>
       </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
         <v>1988</v>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>2598</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>1170</v>
-      </c>
-      <c r="G90" t="n">
-        <v>2641</v>
       </c>
     </row>
     <row r="91">
@@ -9933,19 +10133,19 @@
         <v>6848</v>
       </c>
       <c r="C91" t="n">
+        <v>2685</v>
+      </c>
+      <c r="D91" t="n">
         <v>1795</v>
       </c>
-      <c r="D91" t="n">
+      <c r="E91" t="n">
         <v>1988</v>
       </c>
-      <c r="E91" t="n">
+      <c r="F91" t="n">
         <v>2598</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>1225</v>
-      </c>
-      <c r="G91" t="n">
-        <v>2685</v>
       </c>
     </row>
     <row r="92">
@@ -9958,19 +10158,19 @@
         <v>6848</v>
       </c>
       <c r="C92" t="n">
+        <v>2769</v>
+      </c>
+      <c r="D92" t="n">
         <v>1810</v>
       </c>
-      <c r="D92" t="n">
+      <c r="E92" t="n">
         <v>2176</v>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>2783</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>1298</v>
-      </c>
-      <c r="G92" t="n">
-        <v>2769</v>
       </c>
     </row>
     <row r="93">
@@ -9983,19 +10183,19 @@
         <v>6848</v>
       </c>
       <c r="C93" t="n">
+        <v>2896</v>
+      </c>
+      <c r="D93" t="n">
         <v>1810</v>
       </c>
-      <c r="D93" t="n">
+      <c r="E93" t="n">
         <v>2173</v>
       </c>
-      <c r="E93" t="n">
+      <c r="F93" t="n">
         <v>2783</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>1352</v>
-      </c>
-      <c r="G93" t="n">
-        <v>2896</v>
       </c>
     </row>
     <row r="94">
@@ -10008,19 +10208,19 @@
         <v>6647</v>
       </c>
       <c r="C94" t="n">
+        <v>2896</v>
+      </c>
+      <c r="D94" t="n">
         <v>1810</v>
       </c>
-      <c r="D94" t="n">
+      <c r="E94" t="n">
         <v>2198</v>
       </c>
-      <c r="E94" t="n">
+      <c r="F94" t="n">
         <v>2756</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>1363</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2896</v>
       </c>
     </row>
     <row r="95">
@@ -10033,19 +10233,19 @@
         <v>6647</v>
       </c>
       <c r="C95" t="n">
+        <v>2852</v>
+      </c>
+      <c r="D95" t="n">
         <v>1836</v>
       </c>
-      <c r="D95" t="n">
+      <c r="E95" t="n">
         <v>2215</v>
       </c>
-      <c r="E95" t="n">
+      <c r="F95" t="n">
         <v>2756</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>1453</v>
-      </c>
-      <c r="G95" t="n">
-        <v>2852</v>
       </c>
     </row>
     <row r="96">
@@ -10058,19 +10258,19 @@
         <v>6647</v>
       </c>
       <c r="C96" t="n">
+        <v>2906</v>
+      </c>
+      <c r="D96" t="n">
         <v>1825</v>
       </c>
-      <c r="D96" t="n">
+      <c r="E96" t="n">
         <v>2289</v>
       </c>
-      <c r="E96" t="n">
+      <c r="F96" t="n">
         <v>2759</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>1426</v>
-      </c>
-      <c r="G96" t="n">
-        <v>2906</v>
       </c>
     </row>
     <row r="97">
@@ -10083,19 +10283,19 @@
         <v>6545</v>
       </c>
       <c r="C97" t="n">
+        <v>2950</v>
+      </c>
+      <c r="D97" t="n">
         <v>1892</v>
       </c>
-      <c r="D97" t="n">
+      <c r="E97" t="n">
         <v>2329</v>
       </c>
-      <c r="E97" t="n">
+      <c r="F97" t="n">
         <v>2783</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>1481</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2950</v>
       </c>
     </row>
     <row r="98">
@@ -10108,19 +10308,19 @@
         <v>6545</v>
       </c>
       <c r="C98" t="n">
+        <v>2950</v>
+      </c>
+      <c r="D98" t="n">
         <v>1925</v>
       </c>
-      <c r="D98" t="n">
+      <c r="E98" t="n">
         <v>2329</v>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>2901</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>1503</v>
-      </c>
-      <c r="G98" t="n">
-        <v>2950</v>
       </c>
     </row>
     <row r="99">
@@ -10133,19 +10333,19 @@
         <v>6545</v>
       </c>
       <c r="C99" t="n">
+        <v>2950</v>
+      </c>
+      <c r="D99" t="n">
         <v>2002</v>
       </c>
-      <c r="D99" t="n">
+      <c r="E99" t="n">
         <v>2329</v>
       </c>
-      <c r="E99" t="n">
+      <c r="F99" t="n">
         <v>2792</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>1481</v>
-      </c>
-      <c r="G99" t="n">
-        <v>2950</v>
       </c>
     </row>
     <row r="100">
@@ -10158,19 +10358,19 @@
         <v>6475</v>
       </c>
       <c r="C100" t="n">
+        <v>2882</v>
+      </c>
+      <c r="D100" t="n">
         <v>2118</v>
       </c>
-      <c r="D100" t="n">
+      <c r="E100" t="n">
         <v>2289</v>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>2886</v>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>1414</v>
-      </c>
-      <c r="G100" t="n">
-        <v>2882</v>
       </c>
     </row>
     <row r="101">
@@ -10183,19 +10383,19 @@
         <v>6475</v>
       </c>
       <c r="C101" t="n">
+        <v>2882</v>
+      </c>
+      <c r="D101" t="n">
         <v>2118</v>
       </c>
-      <c r="D101" t="n">
+      <c r="E101" t="n">
         <v>2289</v>
       </c>
-      <c r="E101" t="n">
+      <c r="F101" t="n">
         <v>2906</v>
       </c>
-      <c r="F101" t="n">
+      <c r="G101" t="n">
         <v>1447</v>
-      </c>
-      <c r="G101" t="n">
-        <v>2882</v>
       </c>
     </row>
     <row r="102">
@@ -10208,19 +10408,19 @@
         <v>6475</v>
       </c>
       <c r="C102" t="n">
+        <v>2882</v>
+      </c>
+      <c r="D102" t="n">
         <v>2148</v>
       </c>
-      <c r="D102" t="n">
+      <c r="E102" t="n">
         <v>2289</v>
       </c>
-      <c r="E102" t="n">
+      <c r="F102" t="n">
         <v>2903</v>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>1463</v>
-      </c>
-      <c r="G102" t="n">
-        <v>2882</v>
       </c>
     </row>
     <row r="103">
@@ -10233,19 +10433,19 @@
         <v>6475</v>
       </c>
       <c r="C103" t="n">
+        <v>2882</v>
+      </c>
+      <c r="D103" t="n">
         <v>2187</v>
       </c>
-      <c r="D103" t="n">
+      <c r="E103" t="n">
         <v>2329</v>
       </c>
-      <c r="E103" t="n">
+      <c r="F103" t="n">
         <v>2903</v>
       </c>
-      <c r="F103" t="n">
+      <c r="G103" t="n">
         <v>1477</v>
-      </c>
-      <c r="G103" t="n">
-        <v>2882</v>
       </c>
     </row>
     <row r="104">
@@ -10258,19 +10458,19 @@
         <v>6708</v>
       </c>
       <c r="C104" t="n">
+        <v>2882</v>
+      </c>
+      <c r="D104" t="n">
         <v>2196</v>
       </c>
-      <c r="D104" t="n">
+      <c r="E104" t="n">
         <v>2329</v>
       </c>
-      <c r="E104" t="n">
+      <c r="F104" t="n">
         <v>2903</v>
       </c>
-      <c r="F104" t="n">
+      <c r="G104" t="n">
         <v>1477</v>
-      </c>
-      <c r="G104" t="n">
-        <v>2882</v>
       </c>
     </row>
     <row r="105">
@@ -10283,19 +10483,19 @@
         <v>6708</v>
       </c>
       <c r="C105" t="n">
+        <v>3526</v>
+      </c>
+      <c r="D105" t="n">
         <v>2369</v>
       </c>
-      <c r="D105" t="n">
+      <c r="E105" t="n">
         <v>2207</v>
       </c>
-      <c r="E105" t="n">
+      <c r="F105" t="n">
         <v>4348</v>
       </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>1710</v>
-      </c>
-      <c r="G105" t="n">
-        <v>3526</v>
       </c>
     </row>
     <row r="106">
@@ -10308,19 +10508,19 @@
         <v>6708</v>
       </c>
       <c r="C106" t="n">
+        <v>2920</v>
+      </c>
+      <c r="D106" t="n">
         <v>2227</v>
       </c>
-      <c r="D106" t="n">
+      <c r="E106" t="n">
         <v>2356</v>
       </c>
-      <c r="E106" t="n">
+      <c r="F106" t="n">
         <v>2919</v>
       </c>
-      <c r="F106" t="n">
+      <c r="G106" t="n">
         <v>1505</v>
-      </c>
-      <c r="G106" t="n">
-        <v>2920</v>
       </c>
     </row>
     <row r="107">
@@ -10333,19 +10533,19 @@
         <v>6708</v>
       </c>
       <c r="C107" t="n">
+        <v>2964</v>
+      </c>
+      <c r="D107" t="n">
         <v>2273</v>
       </c>
-      <c r="D107" t="n">
+      <c r="E107" t="n">
         <v>2397</v>
       </c>
-      <c r="E107" t="n">
+      <c r="F107" t="n">
         <v>2966</v>
       </c>
-      <c r="F107" t="n">
+      <c r="G107" t="n">
         <v>1489</v>
-      </c>
-      <c r="G107" t="n">
-        <v>2964</v>
       </c>
     </row>
     <row r="108">
@@ -10358,19 +10558,19 @@
         <v>6708</v>
       </c>
       <c r="C108" t="n">
+        <v>2951</v>
+      </c>
+      <c r="D108" t="n">
         <v>2295</v>
       </c>
-      <c r="D108" t="n">
+      <c r="E108" t="n">
         <v>2439</v>
       </c>
-      <c r="E108" t="n">
+      <c r="F108" t="n">
         <v>3058</v>
       </c>
-      <c r="F108" t="n">
+      <c r="G108" t="n">
         <v>1516</v>
-      </c>
-      <c r="G108" t="n">
-        <v>2951</v>
       </c>
     </row>
     <row r="109">
@@ -10383,19 +10583,19 @@
         <v>6708</v>
       </c>
       <c r="C109" t="n">
+        <v>3386</v>
+      </c>
+      <c r="D109" t="n">
         <v>2466</v>
       </c>
-      <c r="D109" t="n">
+      <c r="E109" t="n">
         <v>2373</v>
       </c>
-      <c r="E109" t="n">
+      <c r="F109" t="n">
         <v>3285</v>
       </c>
-      <c r="F109" t="n">
+      <c r="G109" t="n">
         <v>1463</v>
-      </c>
-      <c r="G109" t="n">
-        <v>3386</v>
       </c>
     </row>
     <row r="110">
@@ -10408,19 +10608,19 @@
         <v>6708</v>
       </c>
       <c r="C110" t="n">
+        <v>3386</v>
+      </c>
+      <c r="D110" t="n">
         <v>2334</v>
       </c>
-      <c r="D110" t="n">
+      <c r="E110" t="n">
         <v>2403</v>
       </c>
-      <c r="E110" t="n">
+      <c r="F110" t="n">
         <v>3316</v>
       </c>
-      <c r="F110" t="n">
+      <c r="G110" t="n">
         <v>1485</v>
-      </c>
-      <c r="G110" t="n">
-        <v>3386</v>
       </c>
     </row>
     <row r="111">
@@ -10433,19 +10633,19 @@
         <v>6708</v>
       </c>
       <c r="C111" t="n">
+        <v>3386</v>
+      </c>
+      <c r="D111" t="n">
         <v>2334</v>
       </c>
-      <c r="D111" t="n">
+      <c r="E111" t="n">
         <v>2403</v>
       </c>
-      <c r="E111" t="n">
+      <c r="F111" t="n">
         <v>3724</v>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>1488</v>
-      </c>
-      <c r="G111" t="n">
-        <v>3386</v>
       </c>
     </row>
     <row r="112">
@@ -10458,19 +10658,19 @@
         <v>6708</v>
       </c>
       <c r="C112" t="n">
+        <v>3386</v>
+      </c>
+      <c r="D112" t="n">
         <v>2210</v>
       </c>
-      <c r="D112" t="n">
+      <c r="E112" t="n">
         <v>2265</v>
       </c>
-      <c r="E112" t="n">
+      <c r="F112" t="n">
         <v>3665</v>
       </c>
-      <c r="F112" t="n">
+      <c r="G112" t="n">
         <v>1458</v>
-      </c>
-      <c r="G112" t="n">
-        <v>3386</v>
       </c>
     </row>
     <row r="113">
@@ -10483,19 +10683,19 @@
         <v>6708</v>
       </c>
       <c r="C113" t="n">
+        <v>3531</v>
+      </c>
+      <c r="D113" t="n">
         <v>2181</v>
       </c>
-      <c r="D113" t="n">
+      <c r="E113" t="n">
         <v>2238</v>
       </c>
-      <c r="E113" t="n">
+      <c r="F113" t="n">
         <v>3577</v>
       </c>
-      <c r="F113" t="n">
+      <c r="G113" t="n">
         <v>1543</v>
-      </c>
-      <c r="G113" t="n">
-        <v>3531</v>
       </c>
     </row>
     <row r="114">
@@ -10508,19 +10708,19 @@
         <v>6708</v>
       </c>
       <c r="C114" t="n">
+        <v>3531</v>
+      </c>
+      <c r="D114" t="n">
         <v>2146</v>
       </c>
-      <c r="D114" t="n">
+      <c r="E114" t="n">
         <v>2238</v>
       </c>
-      <c r="E114" t="n">
+      <c r="F114" t="n">
         <v>3577</v>
       </c>
-      <c r="F114" t="n">
+      <c r="G114" t="n">
         <v>1543</v>
-      </c>
-      <c r="G114" t="n">
-        <v>3531</v>
       </c>
     </row>
     <row r="115">
@@ -10533,19 +10733,19 @@
         <v>6708</v>
       </c>
       <c r="C115" t="n">
+        <v>3521</v>
+      </c>
+      <c r="D115" t="n">
         <v>2356</v>
       </c>
-      <c r="D115" t="n">
+      <c r="E115" t="n">
         <v>2359</v>
       </c>
-      <c r="E115" t="n">
+      <c r="F115" t="n">
         <v>3625</v>
       </c>
-      <c r="F115" t="n">
+      <c r="G115" t="n">
         <v>1685</v>
-      </c>
-      <c r="G115" t="n">
-        <v>3521</v>
       </c>
     </row>
     <row r="116">
@@ -10558,19 +10758,19 @@
         <v>6708</v>
       </c>
       <c r="C116" t="n">
+        <v>3558</v>
+      </c>
+      <c r="D116" t="n">
         <v>2384</v>
       </c>
-      <c r="D116" t="n">
+      <c r="E116" t="n">
         <v>2387</v>
       </c>
-      <c r="E116" t="n">
+      <c r="F116" t="n">
         <v>3644</v>
       </c>
-      <c r="F116" t="n">
+      <c r="G116" t="n">
         <v>1697</v>
-      </c>
-      <c r="G116" t="n">
-        <v>3558</v>
       </c>
     </row>
     <row r="117">
@@ -10583,19 +10783,19 @@
         <v>6708</v>
       </c>
       <c r="C117" t="n">
+        <v>3558</v>
+      </c>
+      <c r="D117" t="n">
         <v>2356</v>
       </c>
-      <c r="D117" t="n">
+      <c r="E117" t="n">
         <v>2242</v>
       </c>
-      <c r="E117" t="n">
+      <c r="F117" t="n">
         <v>3690</v>
       </c>
-      <c r="F117" t="n">
+      <c r="G117" t="n">
         <v>1646</v>
-      </c>
-      <c r="G117" t="n">
-        <v>3558</v>
       </c>
     </row>
     <row r="118">
@@ -10608,19 +10808,19 @@
         <v>6708</v>
       </c>
       <c r="C118" t="n">
+        <v>3558</v>
+      </c>
+      <c r="D118" t="n">
         <v>2377</v>
       </c>
-      <c r="D118" t="n">
+      <c r="E118" t="n">
         <v>2233</v>
       </c>
-      <c r="E118" t="n">
+      <c r="F118" t="n">
         <v>3797</v>
       </c>
-      <c r="F118" t="n">
+      <c r="G118" t="n">
         <v>1646</v>
-      </c>
-      <c r="G118" t="n">
-        <v>3558</v>
       </c>
     </row>
     <row r="119">
@@ -10633,19 +10833,19 @@
         <v>6708</v>
       </c>
       <c r="C119" t="n">
+        <v>3526</v>
+      </c>
+      <c r="D119" t="n">
         <v>2411</v>
       </c>
-      <c r="D119" t="n">
+      <c r="E119" t="n">
         <v>2233</v>
       </c>
-      <c r="E119" t="n">
+      <c r="F119" t="n">
         <v>3801</v>
       </c>
-      <c r="F119" t="n">
+      <c r="G119" t="n">
         <v>1702</v>
-      </c>
-      <c r="G119" t="n">
-        <v>3526</v>
       </c>
     </row>
     <row r="120">
@@ -10658,19 +10858,19 @@
         <v>6708</v>
       </c>
       <c r="C120" t="n">
+        <v>3526</v>
+      </c>
+      <c r="D120" t="n">
         <v>2432</v>
       </c>
-      <c r="D120" t="n">
+      <c r="E120" t="n">
         <v>2233</v>
       </c>
-      <c r="E120" t="n">
+      <c r="F120" t="n">
         <v>4212</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>1710</v>
-      </c>
-      <c r="G120" t="n">
-        <v>3526</v>
       </c>
     </row>
     <row r="121">
@@ -10683,19 +10883,19 @@
         <v>6708</v>
       </c>
       <c r="C121" t="n">
+        <v>3526</v>
+      </c>
+      <c r="D121" t="n">
         <v>2369</v>
       </c>
-      <c r="D121" t="n">
+      <c r="E121" t="n">
         <v>2207</v>
       </c>
-      <c r="E121" t="n">
+      <c r="F121" t="n">
         <v>4348</v>
       </c>
-      <c r="F121" t="n">
+      <c r="G121" t="n">
         <v>1710</v>
-      </c>
-      <c r="G121" t="n">
-        <v>3526</v>
       </c>
     </row>
     <row r="122">
@@ -10708,19 +10908,19 @@
         <v>6708</v>
       </c>
       <c r="C122" t="n">
+        <v>3526</v>
+      </c>
+      <c r="D122" t="n">
         <v>2479</v>
       </c>
-      <c r="D122" t="n">
+      <c r="E122" t="n">
         <v>2207</v>
       </c>
-      <c r="E122" t="n">
+      <c r="F122" t="n">
         <v>4427</v>
       </c>
-      <c r="F122" t="n">
+      <c r="G122" t="n">
         <v>1671</v>
-      </c>
-      <c r="G122" t="n">
-        <v>3526</v>
       </c>
     </row>
     <row r="123">
@@ -10733,19 +10933,19 @@
         <v>6708</v>
       </c>
       <c r="C123" t="n">
+        <v>3907</v>
+      </c>
+      <c r="D123" t="n">
         <v>2611</v>
       </c>
-      <c r="D123" t="n">
+      <c r="E123" t="n">
         <v>2176</v>
       </c>
-      <c r="E123" t="n">
+      <c r="F123" t="n">
         <v>4757</v>
       </c>
-      <c r="F123" t="n">
+      <c r="G123" t="n">
         <v>1685</v>
-      </c>
-      <c r="G123" t="n">
-        <v>3907</v>
       </c>
     </row>
     <row r="124">
@@ -10758,19 +10958,19 @@
         <v>6708</v>
       </c>
       <c r="C124" t="n">
+        <v>4167</v>
+      </c>
+      <c r="D124" t="n">
         <v>2611</v>
       </c>
-      <c r="D124" t="n">
+      <c r="E124" t="n">
         <v>2223</v>
       </c>
-      <c r="E124" t="n">
+      <c r="F124" t="n">
         <v>4994</v>
       </c>
-      <c r="F124" t="n">
+      <c r="G124" t="n">
         <v>1685</v>
-      </c>
-      <c r="G124" t="n">
-        <v>4167</v>
       </c>
     </row>
     <row r="125">
@@ -10783,19 +10983,19 @@
         <v>6708</v>
       </c>
       <c r="C125" t="n">
+        <v>4260</v>
+      </c>
+      <c r="D125" t="n">
         <v>2760</v>
       </c>
-      <c r="D125" t="n">
+      <c r="E125" t="n">
         <v>2223</v>
       </c>
-      <c r="E125" t="n">
+      <c r="F125" t="n">
         <v>5238</v>
       </c>
-      <c r="F125" t="n">
+      <c r="G125" t="n">
         <v>1685</v>
-      </c>
-      <c r="G125" t="n">
-        <v>4260</v>
       </c>
     </row>
     <row r="126">
@@ -10808,19 +11008,19 @@
         <v>6708</v>
       </c>
       <c r="C126" t="n">
+        <v>4260</v>
+      </c>
+      <c r="D126" t="n">
         <v>2805</v>
       </c>
-      <c r="D126" t="n">
+      <c r="E126" t="n">
         <v>2223</v>
       </c>
-      <c r="E126" t="n">
+      <c r="F126" t="n">
         <v>5264</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>1691</v>
-      </c>
-      <c r="G126" t="n">
-        <v>4260</v>
       </c>
     </row>
     <row r="127">
@@ -10833,19 +11033,19 @@
         <v>6708</v>
       </c>
       <c r="C127" t="n">
+        <v>4260</v>
+      </c>
+      <c r="D127" t="n">
         <v>2848</v>
       </c>
-      <c r="D127" t="n">
+      <c r="E127" t="n">
         <v>2250</v>
       </c>
-      <c r="E127" t="n">
+      <c r="F127" t="n">
         <v>5226</v>
       </c>
-      <c r="F127" t="n">
+      <c r="G127" t="n">
         <v>1707</v>
-      </c>
-      <c r="G127" t="n">
-        <v>4260</v>
       </c>
     </row>
     <row r="128">
@@ -10858,19 +11058,19 @@
         <v>6708</v>
       </c>
       <c r="C128" t="n">
+        <v>4292</v>
+      </c>
+      <c r="D128" t="n">
         <v>3837</v>
       </c>
-      <c r="D128" t="n">
+      <c r="E128" t="n">
         <v>2250</v>
       </c>
-      <c r="E128" t="n">
+      <c r="F128" t="n">
         <v>5332</v>
       </c>
-      <c r="F128" t="n">
+      <c r="G128" t="n">
         <v>1651</v>
-      </c>
-      <c r="G128" t="n">
-        <v>4292</v>
       </c>
     </row>
     <row r="129">
@@ -10883,19 +11083,19 @@
         <v>6708</v>
       </c>
       <c r="C129" t="n">
+        <v>4260</v>
+      </c>
+      <c r="D129" t="n">
         <v>4055</v>
       </c>
-      <c r="D129" t="n">
+      <c r="E129" t="n">
         <v>2270</v>
       </c>
-      <c r="E129" t="n">
+      <c r="F129" t="n">
         <v>5332</v>
       </c>
-      <c r="F129" t="n">
+      <c r="G129" t="n">
         <v>1667</v>
-      </c>
-      <c r="G129" t="n">
-        <v>4260</v>
       </c>
     </row>
     <row r="130">
@@ -10908,19 +11108,19 @@
         <v>6708</v>
       </c>
       <c r="C130" t="n">
+        <v>4283</v>
+      </c>
+      <c r="D130" t="n">
         <v>4184</v>
       </c>
-      <c r="D130" t="n">
+      <c r="E130" t="n">
         <v>2270</v>
       </c>
-      <c r="E130" t="n">
+      <c r="F130" t="n">
         <v>5332</v>
       </c>
-      <c r="F130" t="n">
+      <c r="G130" t="n">
         <v>1667</v>
-      </c>
-      <c r="G130" t="n">
-        <v>4283</v>
       </c>
     </row>
     <row r="131">
@@ -10933,19 +11133,19 @@
         <v>6708</v>
       </c>
       <c r="C131" t="n">
+        <v>4322</v>
+      </c>
+      <c r="D131" t="n">
         <v>3625</v>
       </c>
-      <c r="D131" t="n">
+      <c r="E131" t="n">
         <v>2270</v>
       </c>
-      <c r="E131" t="n">
+      <c r="F131" t="n">
         <v>5352</v>
       </c>
-      <c r="F131" t="n">
+      <c r="G131" t="n">
         <v>1665</v>
-      </c>
-      <c r="G131" t="n">
-        <v>4322</v>
       </c>
     </row>
     <row r="132">
@@ -10958,19 +11158,19 @@
         <v>6708</v>
       </c>
       <c r="C132" t="n">
+        <v>4764</v>
+      </c>
+      <c r="D132" t="n">
         <v>3318</v>
       </c>
-      <c r="D132" t="n">
+      <c r="E132" t="n">
         <v>2329</v>
       </c>
-      <c r="E132" t="n">
+      <c r="F132" t="n">
         <v>5166</v>
       </c>
-      <c r="F132" t="n">
+      <c r="G132" t="n">
         <v>1665</v>
-      </c>
-      <c r="G132" t="n">
-        <v>4764</v>
       </c>
     </row>
     <row r="133">
@@ -10983,19 +11183,19 @@
         <v>6708</v>
       </c>
       <c r="C133" t="n">
+        <v>4640</v>
+      </c>
+      <c r="D133" t="n">
         <v>3189</v>
       </c>
-      <c r="D133" t="n">
+      <c r="E133" t="n">
         <v>2624</v>
       </c>
-      <c r="E133" t="n">
+      <c r="F133" t="n">
         <v>5111</v>
       </c>
-      <c r="F133" t="n">
+      <c r="G133" t="n">
         <v>1768</v>
-      </c>
-      <c r="G133" t="n">
-        <v>4640</v>
       </c>
     </row>
     <row r="134">
@@ -11008,19 +11208,19 @@
         <v>6708</v>
       </c>
       <c r="C134" t="n">
+        <v>4603</v>
+      </c>
+      <c r="D134" t="n">
         <v>2972</v>
       </c>
-      <c r="D134" t="n">
+      <c r="E134" t="n">
         <v>2531</v>
       </c>
-      <c r="E134" t="n">
+      <c r="F134" t="n">
         <v>5111</v>
       </c>
-      <c r="F134" t="n">
+      <c r="G134" t="n">
         <v>1666</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4603</v>
       </c>
     </row>
     <row r="135">
@@ -11033,19 +11233,19 @@
         <v>6708</v>
       </c>
       <c r="C135" t="n">
+        <v>4297</v>
+      </c>
+      <c r="D135" t="n">
         <v>2661</v>
       </c>
-      <c r="D135" t="n">
+      <c r="E135" t="n">
         <v>3240</v>
       </c>
-      <c r="E135" t="n">
+      <c r="F135" t="n">
         <v>4127</v>
       </c>
-      <c r="F135" t="n">
+      <c r="G135" t="n">
         <v>1666</v>
-      </c>
-      <c r="G135" t="n">
-        <v>4297</v>
       </c>
     </row>
     <row r="136">
@@ -11058,19 +11258,19 @@
         <v>6708</v>
       </c>
       <c r="C136" t="n">
+        <v>4297</v>
+      </c>
+      <c r="D136" t="n">
         <v>2534</v>
       </c>
-      <c r="D136" t="n">
+      <c r="E136" t="n">
         <v>3387</v>
       </c>
-      <c r="E136" t="n">
+      <c r="F136" t="n">
         <v>4025</v>
       </c>
-      <c r="F136" t="n">
+      <c r="G136" t="n">
         <v>1614</v>
-      </c>
-      <c r="G136" t="n">
-        <v>4297</v>
       </c>
     </row>
     <row r="137">
@@ -11083,19 +11283,19 @@
         <v>6708</v>
       </c>
       <c r="C137" t="n">
+        <v>4138</v>
+      </c>
+      <c r="D137" t="n">
         <v>2154</v>
       </c>
-      <c r="D137" t="n">
+      <c r="E137" t="n">
         <v>3072</v>
       </c>
-      <c r="E137" t="n">
+      <c r="F137" t="n">
         <v>3879</v>
       </c>
-      <c r="F137" t="n">
+      <c r="G137" t="n">
         <v>1511</v>
-      </c>
-      <c r="G137" t="n">
-        <v>4138</v>
       </c>
     </row>
     <row r="138">
@@ -11108,19 +11308,19 @@
         <v>6708</v>
       </c>
       <c r="C138" t="n">
+        <v>3483</v>
+      </c>
+      <c r="D138" t="n">
         <v>2026</v>
       </c>
-      <c r="D138" t="n">
+      <c r="E138" t="n">
         <v>3209</v>
       </c>
-      <c r="E138" t="n">
+      <c r="F138" t="n">
         <v>3524</v>
       </c>
-      <c r="F138" t="n">
+      <c r="G138" t="n">
         <v>1405</v>
-      </c>
-      <c r="G138" t="n">
-        <v>3483</v>
       </c>
     </row>
     <row r="139">
@@ -11133,19 +11333,19 @@
         <v>6612</v>
       </c>
       <c r="C139" t="n">
+        <v>3047</v>
+      </c>
+      <c r="D139" t="n">
         <v>1861</v>
       </c>
-      <c r="D139" t="n">
+      <c r="E139" t="n">
         <v>2995</v>
       </c>
-      <c r="E139" t="n">
+      <c r="F139" t="n">
         <v>3220</v>
       </c>
-      <c r="F139" t="n">
+      <c r="G139" t="n">
         <v>1389</v>
-      </c>
-      <c r="G139" t="n">
-        <v>3047</v>
       </c>
     </row>
     <row r="140">
@@ -11158,19 +11358,19 @@
         <v>6612</v>
       </c>
       <c r="C140" t="n">
+        <v>3047</v>
+      </c>
+      <c r="D140" t="n">
         <v>1861</v>
       </c>
-      <c r="D140" t="n">
+      <c r="E140" t="n">
         <v>2979</v>
       </c>
-      <c r="E140" t="n">
+      <c r="F140" t="n">
         <v>3034</v>
       </c>
-      <c r="F140" t="n">
+      <c r="G140" t="n">
         <v>1406</v>
-      </c>
-      <c r="G140" t="n">
-        <v>3047</v>
       </c>
     </row>
     <row r="141">
@@ -11183,19 +11383,19 @@
         <v>6612</v>
       </c>
       <c r="C141" t="n">
+        <v>3047</v>
+      </c>
+      <c r="D141" t="n">
         <v>1871</v>
       </c>
-      <c r="D141" t="n">
+      <c r="E141" t="n">
         <v>2952</v>
       </c>
-      <c r="E141" t="n">
+      <c r="F141" t="n">
         <v>3115</v>
       </c>
-      <c r="F141" t="n">
+      <c r="G141" t="n">
         <v>1541</v>
-      </c>
-      <c r="G141" t="n">
-        <v>3047</v>
       </c>
     </row>
     <row r="142">
@@ -11208,19 +11408,19 @@
         <v>6612</v>
       </c>
       <c r="C142" t="n">
+        <v>3126</v>
+      </c>
+      <c r="D142" t="n">
         <v>1871</v>
       </c>
-      <c r="D142" t="n">
+      <c r="E142" t="n">
         <v>2917</v>
       </c>
-      <c r="E142" t="n">
+      <c r="F142" t="n">
         <v>3115</v>
       </c>
-      <c r="F142" t="n">
+      <c r="G142" t="n">
         <v>1562</v>
-      </c>
-      <c r="G142" t="n">
-        <v>3126</v>
       </c>
     </row>
     <row r="143">
@@ -11233,19 +11433,19 @@
         <v>6612</v>
       </c>
       <c r="C143" t="n">
+        <v>3084</v>
+      </c>
+      <c r="D143" t="n">
         <v>1871</v>
       </c>
-      <c r="D143" t="n">
+      <c r="E143" t="n">
         <v>2883</v>
       </c>
-      <c r="E143" t="n">
+      <c r="F143" t="n">
         <v>3004</v>
       </c>
-      <c r="F143" t="n">
+      <c r="G143" t="n">
         <v>1562</v>
-      </c>
-      <c r="G143" t="n">
-        <v>3084</v>
       </c>
     </row>
     <row r="144">
@@ -11258,19 +11458,19 @@
         <v>6464</v>
       </c>
       <c r="C144" t="n">
+        <v>3084</v>
+      </c>
+      <c r="D144" t="n">
         <v>1805</v>
       </c>
-      <c r="D144" t="n">
+      <c r="E144" t="n">
         <v>2852</v>
       </c>
-      <c r="E144" t="n">
+      <c r="F144" t="n">
         <v>2940</v>
       </c>
-      <c r="F144" t="n">
+      <c r="G144" t="n">
         <v>1575</v>
-      </c>
-      <c r="G144" t="n">
-        <v>3084</v>
       </c>
     </row>
     <row r="145">
@@ -11283,19 +11483,19 @@
         <v>6464</v>
       </c>
       <c r="C145" t="n">
+        <v>3084</v>
+      </c>
+      <c r="D145" t="n">
         <v>1805</v>
       </c>
-      <c r="D145" t="n">
+      <c r="E145" t="n">
         <v>2852</v>
       </c>
-      <c r="E145" t="n">
+      <c r="F145" t="n">
         <v>2940</v>
       </c>
-      <c r="F145" t="n">
+      <c r="G145" t="n">
         <v>1575</v>
-      </c>
-      <c r="G145" t="n">
-        <v>3084</v>
       </c>
     </row>
     <row r="146">
@@ -11308,19 +11508,19 @@
         <v>6450</v>
       </c>
       <c r="C146" t="n">
+        <v>3089</v>
+      </c>
+      <c r="D146" t="n">
         <v>1843</v>
       </c>
-      <c r="D146" t="n">
+      <c r="E146" t="n">
         <v>2933</v>
       </c>
-      <c r="E146" t="n">
+      <c r="F146" t="n">
         <v>2945</v>
       </c>
-      <c r="F146" t="n">
+      <c r="G146" t="n">
         <v>1532</v>
-      </c>
-      <c r="G146" t="n">
-        <v>3089</v>
       </c>
     </row>
     <row r="147">
@@ -11333,19 +11533,19 @@
         <v>6450</v>
       </c>
       <c r="C147" t="n">
+        <v>2913</v>
+      </c>
+      <c r="D147" t="n">
         <v>1974</v>
       </c>
-      <c r="D147" t="n">
+      <c r="E147" t="n">
         <v>2892</v>
       </c>
-      <c r="E147" t="n">
+      <c r="F147" t="n">
         <v>3210</v>
       </c>
-      <c r="F147" t="n">
+      <c r="G147" t="n">
         <v>1573</v>
-      </c>
-      <c r="G147" t="n">
-        <v>2913</v>
       </c>
     </row>
     <row r="148">
@@ -11358,19 +11558,19 @@
         <v>6450</v>
       </c>
       <c r="C148" t="n">
+        <v>2913</v>
+      </c>
+      <c r="D148" t="n">
         <v>1984</v>
       </c>
-      <c r="D148" t="n">
+      <c r="E148" t="n">
         <v>2892</v>
       </c>
-      <c r="E148" t="n">
+      <c r="F148" t="n">
         <v>3127</v>
       </c>
-      <c r="F148" t="n">
+      <c r="G148" t="n">
         <v>1565</v>
-      </c>
-      <c r="G148" t="n">
-        <v>2913</v>
       </c>
     </row>
     <row r="149">
@@ -11383,19 +11583,19 @@
         <v>6450</v>
       </c>
       <c r="C149" t="n">
+        <v>2850</v>
+      </c>
+      <c r="D149" t="n">
         <v>1917</v>
       </c>
-      <c r="D149" t="n">
+      <c r="E149" t="n">
         <v>2842</v>
       </c>
-      <c r="E149" t="n">
+      <c r="F149" t="n">
         <v>3135</v>
       </c>
-      <c r="F149" t="n">
+      <c r="G149" t="n">
         <v>1538</v>
-      </c>
-      <c r="G149" t="n">
-        <v>2850</v>
       </c>
     </row>
     <row r="150">
@@ -11408,19 +11608,19 @@
         <v>6450</v>
       </c>
       <c r="C150" t="n">
+        <v>2850</v>
+      </c>
+      <c r="D150" t="n">
         <v>1917</v>
       </c>
-      <c r="D150" t="n">
+      <c r="E150" t="n">
         <v>2842</v>
       </c>
-      <c r="E150" t="n">
+      <c r="F150" t="n">
         <v>3219</v>
       </c>
-      <c r="F150" t="n">
+      <c r="G150" t="n">
         <v>1517</v>
-      </c>
-      <c r="G150" t="n">
-        <v>2850</v>
       </c>
     </row>
     <row r="151">
@@ -11433,19 +11633,19 @@
         <v>6450</v>
       </c>
       <c r="C151" t="n">
+        <v>2850</v>
+      </c>
+      <c r="D151" t="n">
         <v>1857</v>
       </c>
-      <c r="D151" t="n">
+      <c r="E151" t="n">
         <v>2808</v>
       </c>
-      <c r="E151" t="n">
+      <c r="F151" t="n">
         <v>3219</v>
       </c>
-      <c r="F151" t="n">
+      <c r="G151" t="n">
         <v>1525</v>
-      </c>
-      <c r="G151" t="n">
-        <v>2850</v>
       </c>
     </row>
     <row r="152">
@@ -11458,19 +11658,19 @@
         <v>6450</v>
       </c>
       <c r="C152" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D152" t="n">
         <v>1935</v>
       </c>
-      <c r="D152" t="n">
+      <c r="E152" t="n">
         <v>2832</v>
       </c>
-      <c r="E152" t="n">
+      <c r="F152" t="n">
         <v>3252</v>
       </c>
-      <c r="F152" t="n">
+      <c r="G152" t="n">
         <v>1525</v>
-      </c>
-      <c r="G152" t="n">
-        <v>2880</v>
       </c>
     </row>
     <row r="153">
@@ -11483,19 +11683,19 @@
         <v>6450</v>
       </c>
       <c r="C153" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D153" t="n">
         <v>1935</v>
       </c>
-      <c r="D153" t="n">
+      <c r="E153" t="n">
         <v>2832</v>
       </c>
-      <c r="E153" t="n">
+      <c r="F153" t="n">
         <v>3252</v>
       </c>
-      <c r="F153" t="n">
+      <c r="G153" t="n">
         <v>1525</v>
-      </c>
-      <c r="G153" t="n">
-        <v>2880</v>
       </c>
     </row>
     <row r="154">
@@ -11508,19 +11708,19 @@
         <v>6612</v>
       </c>
       <c r="C154" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D154" t="n">
         <v>2037</v>
       </c>
-      <c r="D154" t="n">
+      <c r="E154" t="n">
         <v>2832</v>
       </c>
-      <c r="E154" t="n">
+      <c r="F154" t="n">
         <v>3214</v>
       </c>
-      <c r="F154" t="n">
+      <c r="G154" t="n">
         <v>1525</v>
-      </c>
-      <c r="G154" t="n">
-        <v>2880</v>
       </c>
     </row>
     <row r="155">
@@ -11533,19 +11733,19 @@
         <v>6612</v>
       </c>
       <c r="C155" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D155" t="n">
         <v>2062</v>
       </c>
-      <c r="D155" t="n">
+      <c r="E155" t="n">
         <v>2689</v>
       </c>
-      <c r="E155" t="n">
+      <c r="F155" t="n">
         <v>3181</v>
       </c>
-      <c r="F155" t="n">
+      <c r="G155" t="n">
         <v>1508</v>
-      </c>
-      <c r="G155" t="n">
-        <v>2880</v>
       </c>
     </row>
     <row r="156">
@@ -11558,19 +11758,19 @@
         <v>6612</v>
       </c>
       <c r="C156" t="n">
+        <v>2881</v>
+      </c>
+      <c r="D156" t="n">
         <v>2051</v>
       </c>
-      <c r="D156" t="n">
+      <c r="E156" t="n">
         <v>2776</v>
       </c>
-      <c r="E156" t="n">
+      <c r="F156" t="n">
         <v>3257</v>
       </c>
-      <c r="F156" t="n">
+      <c r="G156" t="n">
         <v>1568</v>
-      </c>
-      <c r="G156" t="n">
-        <v>2881</v>
       </c>
     </row>
     <row r="157">
@@ -11583,19 +11783,19 @@
         <v>6612</v>
       </c>
       <c r="C157" t="n">
+        <v>2881</v>
+      </c>
+      <c r="D157" t="n">
         <v>2058</v>
       </c>
-      <c r="D157" t="n">
+      <c r="E157" t="n">
         <v>2836</v>
       </c>
-      <c r="E157" t="n">
+      <c r="F157" t="n">
         <v>3278</v>
       </c>
-      <c r="F157" t="n">
+      <c r="G157" t="n">
         <v>1568</v>
-      </c>
-      <c r="G157" t="n">
-        <v>2881</v>
       </c>
     </row>
     <row r="158">
@@ -11608,19 +11808,19 @@
         <v>6463</v>
       </c>
       <c r="C158" t="n">
+        <v>2784</v>
+      </c>
+      <c r="D158" t="n">
         <v>2093</v>
       </c>
-      <c r="D158" t="n">
+      <c r="E158" t="n">
         <v>2870</v>
       </c>
-      <c r="E158" t="n">
+      <c r="F158" t="n">
         <v>3424</v>
       </c>
-      <c r="F158" t="n">
+      <c r="G158" t="n">
         <v>1568</v>
-      </c>
-      <c r="G158" t="n">
-        <v>2784</v>
       </c>
     </row>
     <row r="159">
@@ -11633,19 +11833,19 @@
         <v>6463</v>
       </c>
       <c r="C159" t="n">
+        <v>2881</v>
+      </c>
+      <c r="D159" t="n">
         <v>2093</v>
       </c>
-      <c r="D159" t="n">
+      <c r="E159" t="n">
         <v>2870</v>
       </c>
-      <c r="E159" t="n">
+      <c r="F159" t="n">
         <v>3473</v>
       </c>
-      <c r="F159" t="n">
+      <c r="G159" t="n">
         <v>1599</v>
-      </c>
-      <c r="G159" t="n">
-        <v>2881</v>
       </c>
     </row>
     <row r="160">
@@ -11658,19 +11858,19 @@
         <v>6463</v>
       </c>
       <c r="C160" t="n">
+        <v>2881</v>
+      </c>
+      <c r="D160" t="n">
         <v>2093</v>
       </c>
-      <c r="D160" t="n">
+      <c r="E160" t="n">
         <v>2787</v>
       </c>
-      <c r="E160" t="n">
+      <c r="F160" t="n">
         <v>3468</v>
       </c>
-      <c r="F160" t="n">
+      <c r="G160" t="n">
         <v>1608</v>
-      </c>
-      <c r="G160" t="n">
-        <v>2881</v>
       </c>
     </row>
     <row r="161">
@@ -11683,19 +11883,19 @@
         <v>6541</v>
       </c>
       <c r="C161" t="n">
+        <v>2772</v>
+      </c>
+      <c r="D161" t="n">
         <v>2130</v>
       </c>
-      <c r="D161" t="n">
+      <c r="E161" t="n">
         <v>2767</v>
       </c>
-      <c r="E161" t="n">
+      <c r="F161" t="n">
         <v>3446</v>
       </c>
-      <c r="F161" t="n">
+      <c r="G161" t="n">
         <v>1608</v>
-      </c>
-      <c r="G161" t="n">
-        <v>2772</v>
       </c>
     </row>
     <row r="162">
@@ -11708,19 +11908,19 @@
         <v>6476</v>
       </c>
       <c r="C162" t="n">
+        <v>2770</v>
+      </c>
+      <c r="D162" t="n">
         <v>2133</v>
       </c>
-      <c r="D162" t="n">
+      <c r="E162" t="n">
         <v>2791</v>
       </c>
-      <c r="E162" t="n">
+      <c r="F162" t="n">
         <v>3446</v>
       </c>
-      <c r="F162" t="n">
+      <c r="G162" t="n">
         <v>1639</v>
-      </c>
-      <c r="G162" t="n">
-        <v>2770</v>
       </c>
     </row>
     <row r="163">
@@ -11733,19 +11933,19 @@
         <v>6478</v>
       </c>
       <c r="C163" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D163" t="n">
         <v>2133</v>
       </c>
-      <c r="D163" t="n">
+      <c r="E163" t="n">
         <v>2871</v>
       </c>
-      <c r="E163" t="n">
+      <c r="F163" t="n">
         <v>3455</v>
       </c>
-      <c r="F163" t="n">
+      <c r="G163" t="n">
         <v>1754</v>
-      </c>
-      <c r="G163" t="n">
-        <v>2886</v>
       </c>
     </row>
     <row r="164">
@@ -11758,19 +11958,19 @@
         <v>6478</v>
       </c>
       <c r="C164" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D164" t="n">
         <v>2221</v>
       </c>
-      <c r="D164" t="n">
+      <c r="E164" t="n">
         <v>2911</v>
       </c>
-      <c r="E164" t="n">
+      <c r="F164" t="n">
         <v>3455</v>
       </c>
-      <c r="F164" t="n">
+      <c r="G164" t="n">
         <v>1847</v>
-      </c>
-      <c r="G164" t="n">
-        <v>2886</v>
       </c>
     </row>
     <row r="165">
@@ -11783,19 +11983,19 @@
         <v>6478</v>
       </c>
       <c r="C165" t="n">
+        <v>2904</v>
+      </c>
+      <c r="D165" t="n">
         <v>2368</v>
       </c>
-      <c r="D165" t="n">
+      <c r="E165" t="n">
         <v>2911</v>
       </c>
-      <c r="E165" t="n">
+      <c r="F165" t="n">
         <v>3508</v>
       </c>
-      <c r="F165" t="n">
+      <c r="G165" t="n">
         <v>1866</v>
-      </c>
-      <c r="G165" t="n">
-        <v>2904</v>
       </c>
     </row>
     <row r="166">
@@ -11808,19 +12008,19 @@
         <v>6565</v>
       </c>
       <c r="C166" t="n">
+        <v>2980</v>
+      </c>
+      <c r="D166" t="n">
         <v>2378</v>
       </c>
-      <c r="D166" t="n">
+      <c r="E166" t="n">
         <v>2911</v>
       </c>
-      <c r="E166" t="n">
+      <c r="F166" t="n">
         <v>3573</v>
       </c>
-      <c r="F166" t="n">
+      <c r="G166" t="n">
         <v>1866</v>
-      </c>
-      <c r="G166" t="n">
-        <v>2980</v>
       </c>
     </row>
     <row r="167">
@@ -11833,19 +12033,19 @@
         <v>6565</v>
       </c>
       <c r="C167" t="n">
+        <v>3016</v>
+      </c>
+      <c r="D167" t="n">
         <v>2378</v>
       </c>
-      <c r="D167" t="n">
+      <c r="E167" t="n">
         <v>2911</v>
       </c>
-      <c r="E167" t="n">
+      <c r="F167" t="n">
         <v>3573</v>
       </c>
-      <c r="F167" t="n">
+      <c r="G167" t="n">
         <v>1866</v>
-      </c>
-      <c r="G167" t="n">
-        <v>3016</v>
       </c>
     </row>
     <row r="168">
@@ -11858,19 +12058,19 @@
         <v>6565</v>
       </c>
       <c r="C168" t="n">
+        <v>2980</v>
+      </c>
+      <c r="D168" t="n">
         <v>2299</v>
       </c>
-      <c r="D168" t="n">
+      <c r="E168" t="n">
         <v>2904</v>
       </c>
-      <c r="E168" t="n">
+      <c r="F168" t="n">
         <v>3595</v>
       </c>
-      <c r="F168" t="n">
+      <c r="G168" t="n">
         <v>1840</v>
-      </c>
-      <c r="G168" t="n">
-        <v>2980</v>
       </c>
     </row>
     <row r="169">
@@ -11883,19 +12083,19 @@
         <v>6506</v>
       </c>
       <c r="C169" t="n">
+        <v>3049</v>
+      </c>
+      <c r="D169" t="n">
         <v>2293</v>
       </c>
-      <c r="D169" t="n">
+      <c r="E169" t="n">
         <v>2791</v>
       </c>
-      <c r="E169" t="n">
+      <c r="F169" t="n">
         <v>3757</v>
       </c>
-      <c r="F169" t="n">
+      <c r="G169" t="n">
         <v>1856</v>
-      </c>
-      <c r="G169" t="n">
-        <v>3049</v>
       </c>
     </row>
     <row r="170">
@@ -11908,19 +12108,19 @@
         <v>6574</v>
       </c>
       <c r="C170" t="n">
+        <v>2940</v>
+      </c>
+      <c r="D170" t="n">
         <v>2293</v>
       </c>
-      <c r="D170" t="n">
+      <c r="E170" t="n">
         <v>2791</v>
       </c>
-      <c r="E170" t="n">
+      <c r="F170" t="n">
         <v>3757</v>
       </c>
-      <c r="F170" t="n">
+      <c r="G170" t="n">
         <v>1922</v>
-      </c>
-      <c r="G170" t="n">
-        <v>2940</v>
       </c>
     </row>
     <row r="171">
@@ -11933,19 +12133,19 @@
         <v>6561</v>
       </c>
       <c r="C171" t="n">
+        <v>2836</v>
+      </c>
+      <c r="D171" t="n">
         <v>2293</v>
       </c>
-      <c r="D171" t="n">
+      <c r="E171" t="n">
         <v>2791</v>
       </c>
-      <c r="E171" t="n">
+      <c r="F171" t="n">
         <v>3719</v>
       </c>
-      <c r="F171" t="n">
+      <c r="G171" t="n">
         <v>1949</v>
-      </c>
-      <c r="G171" t="n">
-        <v>2836</v>
       </c>
     </row>
     <row r="172">
@@ -11958,19 +12158,19 @@
         <v>6539</v>
       </c>
       <c r="C172" t="n">
+        <v>2798</v>
+      </c>
+      <c r="D172" t="n">
         <v>2235</v>
       </c>
-      <c r="D172" t="n">
+      <c r="E172" t="n">
         <v>2727</v>
       </c>
-      <c r="E172" t="n">
+      <c r="F172" t="n">
         <v>3757</v>
       </c>
-      <c r="F172" t="n">
+      <c r="G172" t="n">
         <v>1939</v>
-      </c>
-      <c r="G172" t="n">
-        <v>2798</v>
       </c>
     </row>
     <row r="173">
@@ -11983,19 +12183,19 @@
         <v>6539</v>
       </c>
       <c r="C173" t="n">
+        <v>2798</v>
+      </c>
+      <c r="D173" t="n">
         <v>2418</v>
       </c>
-      <c r="D173" t="n">
+      <c r="E173" t="n">
         <v>2751</v>
       </c>
-      <c r="E173" t="n">
+      <c r="F173" t="n">
         <v>3757</v>
       </c>
-      <c r="F173" t="n">
+      <c r="G173" t="n">
         <v>1939</v>
-      </c>
-      <c r="G173" t="n">
-        <v>2798</v>
       </c>
     </row>
     <row r="174">
@@ -12008,19 +12208,19 @@
         <v>6426</v>
       </c>
       <c r="C174" t="n">
+        <v>2798</v>
+      </c>
+      <c r="D174" t="n">
         <v>2564</v>
       </c>
-      <c r="D174" t="n">
+      <c r="E174" t="n">
         <v>2751</v>
       </c>
-      <c r="E174" t="n">
+      <c r="F174" t="n">
         <v>3973</v>
       </c>
-      <c r="F174" t="n">
+      <c r="G174" t="n">
         <v>1955</v>
-      </c>
-      <c r="G174" t="n">
-        <v>2798</v>
       </c>
     </row>
     <row r="175">
@@ -12033,19 +12233,19 @@
         <v>6426</v>
       </c>
       <c r="C175" t="n">
+        <v>2854</v>
+      </c>
+      <c r="D175" t="n">
         <v>2687</v>
       </c>
-      <c r="D175" t="n">
+      <c r="E175" t="n">
         <v>3075</v>
       </c>
-      <c r="E175" t="n">
+      <c r="F175" t="n">
         <v>4078</v>
       </c>
-      <c r="F175" t="n">
+      <c r="G175" t="n">
         <v>2013</v>
-      </c>
-      <c r="G175" t="n">
-        <v>2854</v>
       </c>
     </row>
     <row r="176">
@@ -12058,19 +12258,19 @@
         <v>6426</v>
       </c>
       <c r="C176" t="n">
+        <v>2854</v>
+      </c>
+      <c r="D176" t="n">
         <v>2690</v>
       </c>
-      <c r="D176" t="n">
+      <c r="E176" t="n">
         <v>3051</v>
       </c>
-      <c r="E176" t="n">
+      <c r="F176" t="n">
         <v>4599</v>
       </c>
-      <c r="F176" t="n">
+      <c r="G176" t="n">
         <v>2021</v>
-      </c>
-      <c r="G176" t="n">
-        <v>2854</v>
       </c>
     </row>
     <row r="177">
@@ -12083,19 +12283,19 @@
         <v>6389</v>
       </c>
       <c r="C177" t="n">
+        <v>2854</v>
+      </c>
+      <c r="D177" t="n">
         <v>2827</v>
       </c>
-      <c r="D177" t="n">
+      <c r="E177" t="n">
         <v>3089</v>
       </c>
-      <c r="E177" t="n">
+      <c r="F177" t="n">
         <v>4409</v>
       </c>
-      <c r="F177" t="n">
+      <c r="G177" t="n">
         <v>2154</v>
-      </c>
-      <c r="G177" t="n">
-        <v>2854</v>
       </c>
     </row>
     <row r="178">
@@ -12108,19 +12308,19 @@
         <v>6426</v>
       </c>
       <c r="C178" t="n">
+        <v>2855</v>
+      </c>
+      <c r="D178" t="n">
         <v>3013</v>
       </c>
-      <c r="D178" t="n">
+      <c r="E178" t="n">
         <v>3191</v>
       </c>
-      <c r="E178" t="n">
+      <c r="F178" t="n">
         <v>4673</v>
       </c>
-      <c r="F178" t="n">
+      <c r="G178" t="n">
         <v>2215</v>
-      </c>
-      <c r="G178" t="n">
-        <v>2855</v>
       </c>
     </row>
     <row r="179">
@@ -12133,19 +12333,19 @@
         <v>6466</v>
       </c>
       <c r="C179" t="n">
+        <v>3075</v>
+      </c>
+      <c r="D179" t="n">
         <v>3312</v>
       </c>
-      <c r="D179" t="n">
+      <c r="E179" t="n">
         <v>3161</v>
       </c>
-      <c r="E179" t="n">
+      <c r="F179" t="n">
         <v>4953</v>
       </c>
-      <c r="F179" t="n">
+      <c r="G179" t="n">
         <v>2364</v>
-      </c>
-      <c r="G179" t="n">
-        <v>3075</v>
       </c>
     </row>
     <row r="180">
@@ -12158,19 +12358,19 @@
         <v>6466</v>
       </c>
       <c r="C180" t="n">
+        <v>3211</v>
+      </c>
+      <c r="D180" t="n">
         <v>3744</v>
       </c>
-      <c r="D180" t="n">
+      <c r="E180" t="n">
         <v>3254</v>
       </c>
-      <c r="E180" t="n">
+      <c r="F180" t="n">
         <v>4938</v>
       </c>
-      <c r="F180" t="n">
+      <c r="G180" t="n">
         <v>2452</v>
-      </c>
-      <c r="G180" t="n">
-        <v>3211</v>
       </c>
     </row>
     <row r="181">
@@ -12183,19 +12383,19 @@
         <v>6466</v>
       </c>
       <c r="C181" t="n">
+        <v>3402</v>
+      </c>
+      <c r="D181" t="n">
         <v>3469</v>
       </c>
-      <c r="D181" t="n">
+      <c r="E181" t="n">
         <v>3243</v>
       </c>
-      <c r="E181" t="n">
+      <c r="F181" t="n">
         <v>5026</v>
       </c>
-      <c r="F181" t="n">
+      <c r="G181" t="n">
         <v>2512</v>
-      </c>
-      <c r="G181" t="n">
-        <v>3402</v>
       </c>
     </row>
     <row r="182">
@@ -12208,19 +12408,19 @@
         <v>6466</v>
       </c>
       <c r="C182" t="n">
+        <v>3833</v>
+      </c>
+      <c r="D182" t="n">
         <v>2711</v>
       </c>
-      <c r="D182" t="n">
+      <c r="E182" t="n">
         <v>3796</v>
       </c>
-      <c r="E182" t="n">
+      <c r="F182" t="n">
         <v>4924</v>
       </c>
-      <c r="F182" t="n">
+      <c r="G182" t="n">
         <v>2668</v>
-      </c>
-      <c r="G182" t="n">
-        <v>3833</v>
       </c>
     </row>
     <row r="183">
@@ -12233,19 +12433,19 @@
         <v>6466</v>
       </c>
       <c r="C183" t="n">
+        <v>3905</v>
+      </c>
+      <c r="D183" t="n">
         <v>2421</v>
       </c>
-      <c r="D183" t="n">
+      <c r="E183" t="n">
         <v>3999</v>
       </c>
-      <c r="E183" t="n">
+      <c r="F183" t="n">
         <v>4225</v>
       </c>
-      <c r="F183" t="n">
+      <c r="G183" t="n">
         <v>2370</v>
-      </c>
-      <c r="G183" t="n">
-        <v>3905</v>
       </c>
     </row>
     <row r="184">
@@ -12258,19 +12458,19 @@
         <v>6466</v>
       </c>
       <c r="C184" t="n">
+        <v>3751</v>
+      </c>
+      <c r="D184" t="n">
         <v>2306</v>
       </c>
-      <c r="D184" t="n">
+      <c r="E184" t="n">
         <v>3948</v>
       </c>
-      <c r="E184" t="n">
+      <c r="F184" t="n">
         <v>3997</v>
       </c>
-      <c r="F184" t="n">
+      <c r="G184" t="n">
         <v>2411</v>
-      </c>
-      <c r="G184" t="n">
-        <v>3751</v>
       </c>
     </row>
     <row r="185">
@@ -12283,19 +12483,19 @@
         <v>6466</v>
       </c>
       <c r="C185" t="n">
+        <v>3797</v>
+      </c>
+      <c r="D185" t="n">
         <v>2198</v>
       </c>
-      <c r="D185" t="n">
+      <c r="E185" t="n">
         <v>3947</v>
       </c>
-      <c r="E185" t="n">
+      <c r="F185" t="n">
         <v>3783</v>
       </c>
-      <c r="F185" t="n">
+      <c r="G185" t="n">
         <v>2155</v>
-      </c>
-      <c r="G185" t="n">
-        <v>3797</v>
       </c>
     </row>
     <row r="186">
@@ -12308,19 +12508,19 @@
         <v>6534</v>
       </c>
       <c r="C186" t="n">
+        <v>3545</v>
+      </c>
+      <c r="D186" t="n">
         <v>2005</v>
       </c>
-      <c r="D186" t="n">
+      <c r="E186" t="n">
         <v>3795</v>
       </c>
-      <c r="E186" t="n">
+      <c r="F186" t="n">
         <v>3631</v>
       </c>
-      <c r="F186" t="n">
+      <c r="G186" t="n">
         <v>1903</v>
-      </c>
-      <c r="G186" t="n">
-        <v>3545</v>
       </c>
     </row>
     <row r="187">
@@ -12333,19 +12533,19 @@
         <v>6618</v>
       </c>
       <c r="C187" t="n">
+        <v>3289</v>
+      </c>
+      <c r="D187" t="n">
         <v>1971</v>
       </c>
-      <c r="D187" t="n">
+      <c r="E187" t="n">
         <v>3301</v>
       </c>
-      <c r="E187" t="n">
+      <c r="F187" t="n">
         <v>3464</v>
       </c>
-      <c r="F187" t="n">
+      <c r="G187" t="n">
         <v>1710</v>
-      </c>
-      <c r="G187" t="n">
-        <v>3289</v>
       </c>
     </row>
     <row r="188">
@@ -12358,19 +12558,19 @@
         <v>6662</v>
       </c>
       <c r="C188" t="n">
+        <v>2957</v>
+      </c>
+      <c r="D188" t="n">
         <v>1853</v>
       </c>
-      <c r="D188" t="n">
+      <c r="E188" t="n">
         <v>2996</v>
       </c>
-      <c r="E188" t="n">
+      <c r="F188" t="n">
         <v>3406</v>
       </c>
-      <c r="F188" t="n">
+      <c r="G188" t="n">
         <v>1583</v>
-      </c>
-      <c r="G188" t="n">
-        <v>2957</v>
       </c>
     </row>
     <row r="189">
@@ -12383,19 +12583,19 @@
         <v>6872</v>
       </c>
       <c r="C189" t="n">
+        <v>2677</v>
+      </c>
+      <c r="D189" t="n">
         <v>1769</v>
       </c>
-      <c r="D189" t="n">
+      <c r="E189" t="n">
         <v>2662</v>
       </c>
-      <c r="E189" t="n">
+      <c r="F189" t="n">
         <v>3086</v>
       </c>
-      <c r="F189" t="n">
+      <c r="G189" t="n">
         <v>1449</v>
-      </c>
-      <c r="G189" t="n">
-        <v>2677</v>
       </c>
     </row>
     <row r="190">
@@ -12408,19 +12608,19 @@
         <v>6872</v>
       </c>
       <c r="C190" t="n">
+        <v>2476</v>
+      </c>
+      <c r="D190" t="n">
         <v>1906</v>
       </c>
-      <c r="D190" t="n">
+      <c r="E190" t="n">
         <v>2853</v>
       </c>
-      <c r="E190" t="n">
+      <c r="F190" t="n">
         <v>3111</v>
       </c>
-      <c r="F190" t="n">
+      <c r="G190" t="n">
         <v>1437</v>
-      </c>
-      <c r="G190" t="n">
-        <v>2476</v>
       </c>
     </row>
     <row r="191">
@@ -12433,19 +12633,19 @@
         <v>6872</v>
       </c>
       <c r="C191" t="n">
+        <v>2587</v>
+      </c>
+      <c r="D191" t="n">
         <v>2055</v>
       </c>
-      <c r="D191" t="n">
+      <c r="E191" t="n">
         <v>2672</v>
       </c>
-      <c r="E191" t="n">
+      <c r="F191" t="n">
         <v>3171</v>
       </c>
-      <c r="F191" t="n">
+      <c r="G191" t="n">
         <v>1314</v>
-      </c>
-      <c r="G191" t="n">
-        <v>2587</v>
       </c>
     </row>
     <row r="192">
@@ -12458,19 +12658,19 @@
         <v>6872</v>
       </c>
       <c r="C192" t="n">
+        <v>2812</v>
+      </c>
+      <c r="D192" t="n">
         <v>1970</v>
       </c>
-      <c r="D192" t="n">
+      <c r="E192" t="n">
         <v>2410</v>
       </c>
-      <c r="E192" t="n">
+      <c r="F192" t="n">
         <v>3097</v>
       </c>
-      <c r="F192" t="n">
+      <c r="G192" t="n">
         <v>1352</v>
-      </c>
-      <c r="G192" t="n">
-        <v>2812</v>
       </c>
     </row>
     <row r="193">
@@ -12483,19 +12683,19 @@
         <v>7079</v>
       </c>
       <c r="C193" t="n">
+        <v>2740</v>
+      </c>
+      <c r="D193" t="n">
         <v>2027</v>
       </c>
-      <c r="D193" t="n">
+      <c r="E193" t="n">
         <v>2713</v>
       </c>
-      <c r="E193" t="n">
+      <c r="F193" t="n">
         <v>3152</v>
       </c>
-      <c r="F193" t="n">
+      <c r="G193" t="n">
         <v>1412</v>
-      </c>
-      <c r="G193" t="n">
-        <v>2740</v>
       </c>
     </row>
     <row r="194">
@@ -12508,19 +12708,19 @@
         <v>7079</v>
       </c>
       <c r="C194" t="n">
+        <v>2833</v>
+      </c>
+      <c r="D194" t="n">
         <v>2191</v>
       </c>
-      <c r="D194" t="n">
+      <c r="E194" t="n">
         <v>2531</v>
       </c>
-      <c r="E194" t="n">
+      <c r="F194" t="n">
         <v>3053</v>
       </c>
-      <c r="F194" t="n">
+      <c r="G194" t="n">
         <v>1362</v>
-      </c>
-      <c r="G194" t="n">
-        <v>2833</v>
       </c>
     </row>
     <row r="195">
@@ -12533,19 +12733,19 @@
         <v>7017</v>
       </c>
       <c r="C195" t="n">
+        <v>2935</v>
+      </c>
+      <c r="D195" t="n">
         <v>2278</v>
       </c>
-      <c r="D195" t="n">
+      <c r="E195" t="n">
         <v>2410</v>
       </c>
-      <c r="E195" t="n">
+      <c r="F195" t="n">
         <v>3093</v>
       </c>
-      <c r="F195" t="n">
+      <c r="G195" t="n">
         <v>1362</v>
-      </c>
-      <c r="G195" t="n">
-        <v>2935</v>
       </c>
     </row>
     <row r="196">
@@ -12558,19 +12758,19 @@
         <v>6977</v>
       </c>
       <c r="C196" t="n">
+        <v>3037</v>
+      </c>
+      <c r="D196" t="n">
         <v>2271</v>
       </c>
-      <c r="D196" t="n">
+      <c r="E196" t="n">
         <v>2531</v>
       </c>
-      <c r="E196" t="n">
+      <c r="F196" t="n">
         <v>3258</v>
       </c>
-      <c r="F196" t="n">
+      <c r="G196" t="n">
         <v>1352</v>
-      </c>
-      <c r="G196" t="n">
-        <v>3037</v>
       </c>
     </row>
     <row r="197">
@@ -12583,19 +12783,19 @@
         <v>7152</v>
       </c>
       <c r="C197" t="n">
+        <v>3017</v>
+      </c>
+      <c r="D197" t="n">
         <v>2368</v>
       </c>
-      <c r="D197" t="n">
+      <c r="E197" t="n">
         <v>2520</v>
       </c>
-      <c r="E197" t="n">
+      <c r="F197" t="n">
         <v>3329</v>
       </c>
-      <c r="F197" t="n">
+      <c r="G197" t="n">
         <v>1352</v>
-      </c>
-      <c r="G197" t="n">
-        <v>3017</v>
       </c>
     </row>
     <row r="198">
@@ -12608,19 +12808,19 @@
         <v>7152</v>
       </c>
       <c r="C198" t="n">
+        <v>3225</v>
+      </c>
+      <c r="D198" t="n">
         <v>2441</v>
       </c>
-      <c r="D198" t="n">
+      <c r="E198" t="n">
         <v>2553</v>
       </c>
-      <c r="E198" t="n">
+      <c r="F198" t="n">
         <v>3315</v>
       </c>
-      <c r="F198" t="n">
+      <c r="G198" t="n">
         <v>1352</v>
-      </c>
-      <c r="G198" t="n">
-        <v>3225</v>
       </c>
     </row>
     <row r="199">
@@ -12633,19 +12833,19 @@
         <v>7152</v>
       </c>
       <c r="C199" t="n">
+        <v>3314</v>
+      </c>
+      <c r="D199" t="n">
         <v>2435</v>
       </c>
-      <c r="D199" t="n">
+      <c r="E199" t="n">
         <v>2525</v>
       </c>
-      <c r="E199" t="n">
+      <c r="F199" t="n">
         <v>3447</v>
       </c>
-      <c r="F199" t="n">
+      <c r="G199" t="n">
         <v>1362</v>
-      </c>
-      <c r="G199" t="n">
-        <v>3314</v>
       </c>
     </row>
     <row r="200">
@@ -12658,19 +12858,19 @@
         <v>7152</v>
       </c>
       <c r="C200" t="n">
+        <v>3410</v>
+      </c>
+      <c r="D200" t="n">
         <v>2517</v>
       </c>
-      <c r="D200" t="n">
+      <c r="E200" t="n">
         <v>2563</v>
       </c>
-      <c r="E200" t="n">
+      <c r="F200" t="n">
         <v>3545</v>
       </c>
-      <c r="F200" t="n">
+      <c r="G200" t="n">
         <v>1362</v>
-      </c>
-      <c r="G200" t="n">
-        <v>3410</v>
       </c>
     </row>
     <row r="201">
@@ -12683,19 +12883,19 @@
         <v>7238</v>
       </c>
       <c r="C201" t="n">
+        <v>3461</v>
+      </c>
+      <c r="D201" t="n">
         <v>2618</v>
       </c>
-      <c r="D201" t="n">
+      <c r="E201" t="n">
         <v>2418</v>
       </c>
-      <c r="E201" t="n">
+      <c r="F201" t="n">
         <v>3517</v>
       </c>
-      <c r="F201" t="n">
+      <c r="G201" t="n">
         <v>1418</v>
-      </c>
-      <c r="G201" t="n">
-        <v>3461</v>
       </c>
     </row>
     <row r="202">
@@ -12708,19 +12908,19 @@
         <v>7238</v>
       </c>
       <c r="C202" t="n">
+        <v>3429</v>
+      </c>
+      <c r="D202" t="n">
         <v>2763</v>
       </c>
-      <c r="D202" t="n">
+      <c r="E202" t="n">
         <v>2531</v>
       </c>
-      <c r="E202" t="n">
+      <c r="F202" t="n">
         <v>3512</v>
       </c>
-      <c r="F202" t="n">
+      <c r="G202" t="n">
         <v>1367</v>
-      </c>
-      <c r="G202" t="n">
-        <v>3429</v>
       </c>
     </row>
     <row r="203">
@@ -12733,19 +12933,19 @@
         <v>7238</v>
       </c>
       <c r="C203" t="n">
+        <v>3399</v>
+      </c>
+      <c r="D203" t="n">
         <v>2678</v>
       </c>
-      <c r="D203" t="n">
+      <c r="E203" t="n">
         <v>2519</v>
       </c>
-      <c r="E203" t="n">
+      <c r="F203" t="n">
         <v>3637</v>
       </c>
-      <c r="F203" t="n">
+      <c r="G203" t="n">
         <v>1362</v>
-      </c>
-      <c r="G203" t="n">
-        <v>3399</v>
       </c>
     </row>
     <row r="204">
@@ -12758,19 +12958,19 @@
         <v>7152</v>
       </c>
       <c r="C204" t="n">
+        <v>3445</v>
+      </c>
+      <c r="D204" t="n">
         <v>2692</v>
       </c>
-      <c r="D204" t="n">
+      <c r="E204" t="n">
         <v>2458</v>
       </c>
-      <c r="E204" t="n">
+      <c r="F204" t="n">
         <v>3569</v>
       </c>
-      <c r="F204" t="n">
+      <c r="G204" t="n">
         <v>1359</v>
-      </c>
-      <c r="G204" t="n">
-        <v>3445</v>
       </c>
     </row>
     <row r="205">
@@ -12783,19 +12983,19 @@
         <v>7067</v>
       </c>
       <c r="C205" t="n">
+        <v>3458</v>
+      </c>
+      <c r="D205" t="n">
         <v>2811</v>
       </c>
-      <c r="D205" t="n">
+      <c r="E205" t="n">
         <v>2532</v>
       </c>
-      <c r="E205" t="n">
+      <c r="F205" t="n">
         <v>3581</v>
       </c>
-      <c r="F205" t="n">
+      <c r="G205" t="n">
         <v>1359</v>
-      </c>
-      <c r="G205" t="n">
-        <v>3458</v>
       </c>
     </row>
     <row r="206">
@@ -12808,19 +13008,19 @@
         <v>7067</v>
       </c>
       <c r="C206" t="n">
+        <v>3458</v>
+      </c>
+      <c r="D206" t="n">
         <v>2811</v>
       </c>
-      <c r="D206" t="n">
+      <c r="E206" t="n">
         <v>2532</v>
       </c>
-      <c r="E206" t="n">
+      <c r="F206" t="n">
         <v>3581</v>
       </c>
-      <c r="F206" t="n">
+      <c r="G206" t="n">
         <v>1359</v>
-      </c>
-      <c r="G206" t="n">
-        <v>3458</v>
       </c>
     </row>
     <row r="207">
@@ -12833,19 +13033,19 @@
         <v>7067</v>
       </c>
       <c r="C207" t="n">
+        <v>3575</v>
+      </c>
+      <c r="D207" t="n">
         <v>2800</v>
       </c>
-      <c r="D207" t="n">
+      <c r="E207" t="n">
         <v>2557</v>
       </c>
-      <c r="E207" t="n">
+      <c r="F207" t="n">
         <v>3502</v>
       </c>
-      <c r="F207" t="n">
+      <c r="G207" t="n">
         <v>1359</v>
-      </c>
-      <c r="G207" t="n">
-        <v>3575</v>
       </c>
     </row>
     <row r="208">
@@ -12858,19 +13058,19 @@
         <v>7067</v>
       </c>
       <c r="C208" t="n">
+        <v>3642</v>
+      </c>
+      <c r="D208" t="n">
         <v>2766</v>
       </c>
-      <c r="D208" t="n">
+      <c r="E208" t="n">
         <v>2536</v>
       </c>
-      <c r="E208" t="n">
+      <c r="F208" t="n">
         <v>3547</v>
       </c>
-      <c r="F208" t="n">
+      <c r="G208" t="n">
         <v>1359</v>
-      </c>
-      <c r="G208" t="n">
-        <v>3642</v>
       </c>
     </row>
     <row r="209">
@@ -12883,19 +13083,19 @@
         <v>7067</v>
       </c>
       <c r="C209" t="n">
+        <v>3494</v>
+      </c>
+      <c r="D209" t="n">
         <v>2707</v>
       </c>
-      <c r="D209" t="n">
+      <c r="E209" t="n">
         <v>2281</v>
       </c>
-      <c r="E209" t="n">
+      <c r="F209" t="n">
         <v>3482</v>
       </c>
-      <c r="F209" t="n">
+      <c r="G209" t="n">
         <v>1359</v>
-      </c>
-      <c r="G209" t="n">
-        <v>3494</v>
       </c>
     </row>
     <row r="210">
@@ -12908,19 +13108,19 @@
         <v>7110</v>
       </c>
       <c r="C210" t="n">
+        <v>3767</v>
+      </c>
+      <c r="D210" t="n">
         <v>2745</v>
       </c>
-      <c r="D210" t="n">
+      <c r="E210" t="n">
         <v>2565</v>
       </c>
-      <c r="E210" t="n">
+      <c r="F210" t="n">
         <v>3547</v>
       </c>
-      <c r="F210" t="n">
+      <c r="G210" t="n">
         <v>1359</v>
-      </c>
-      <c r="G210" t="n">
-        <v>3767</v>
       </c>
     </row>
     <row r="211">
@@ -12933,19 +13133,19 @@
         <v>7110</v>
       </c>
       <c r="C211" t="n">
+        <v>3736</v>
+      </c>
+      <c r="D211" t="n">
         <v>2862</v>
       </c>
-      <c r="D211" t="n">
+      <c r="E211" t="n">
         <v>2596</v>
       </c>
-      <c r="E211" t="n">
+      <c r="F211" t="n">
         <v>3586</v>
       </c>
-      <c r="F211" t="n">
+      <c r="G211" t="n">
         <v>1359</v>
-      </c>
-      <c r="G211" t="n">
-        <v>3736</v>
       </c>
     </row>
     <row r="212">
@@ -12958,19 +13158,19 @@
         <v>7031</v>
       </c>
       <c r="C212" t="n">
+        <v>3767</v>
+      </c>
+      <c r="D212" t="n">
         <v>2896</v>
       </c>
-      <c r="D212" t="n">
+      <c r="E212" t="n">
         <v>2567</v>
       </c>
-      <c r="E212" t="n">
+      <c r="F212" t="n">
         <v>3586</v>
       </c>
-      <c r="F212" t="n">
+      <c r="G212" t="n">
         <v>1359</v>
-      </c>
-      <c r="G212" t="n">
-        <v>3767</v>
       </c>
     </row>
     <row r="213">
@@ -12983,19 +13183,19 @@
         <v>7031</v>
       </c>
       <c r="C213" t="n">
+        <v>3736</v>
+      </c>
+      <c r="D213" t="n">
         <v>2922</v>
       </c>
-      <c r="D213" t="n">
+      <c r="E213" t="n">
         <v>2645</v>
       </c>
-      <c r="E213" t="n">
+      <c r="F213" t="n">
         <v>3572</v>
       </c>
-      <c r="F213" t="n">
+      <c r="G213" t="n">
         <v>1359</v>
-      </c>
-      <c r="G213" t="n">
-        <v>3736</v>
       </c>
     </row>
     <row r="214">
@@ -13008,19 +13208,19 @@
         <v>6941</v>
       </c>
       <c r="C214" t="n">
+        <v>3802</v>
+      </c>
+      <c r="D214" t="n">
         <v>2949</v>
       </c>
-      <c r="D214" t="n">
+      <c r="E214" t="n">
         <v>2613</v>
       </c>
-      <c r="E214" t="n">
+      <c r="F214" t="n">
         <v>3615</v>
       </c>
-      <c r="F214" t="n">
+      <c r="G214" t="n">
         <v>1359</v>
-      </c>
-      <c r="G214" t="n">
-        <v>3802</v>
       </c>
     </row>
     <row r="215">
@@ -13033,19 +13233,19 @@
         <v>6941</v>
       </c>
       <c r="C215" t="n">
+        <v>3872</v>
+      </c>
+      <c r="D215" t="n">
         <v>2984</v>
       </c>
-      <c r="D215" t="n">
+      <c r="E215" t="n">
         <v>2653</v>
       </c>
-      <c r="E215" t="n">
+      <c r="F215" t="n">
         <v>3679</v>
       </c>
-      <c r="F215" t="n">
+      <c r="G215" t="n">
         <v>1359</v>
-      </c>
-      <c r="G215" t="n">
-        <v>3872</v>
       </c>
     </row>
     <row r="216">
@@ -13058,19 +13258,19 @@
         <v>6984</v>
       </c>
       <c r="C216" t="n">
+        <v>3837</v>
+      </c>
+      <c r="D216" t="n">
         <v>3017</v>
       </c>
-      <c r="D216" t="n">
+      <c r="E216" t="n">
         <v>2712</v>
       </c>
-      <c r="E216" t="n">
+      <c r="F216" t="n">
         <v>3666</v>
       </c>
-      <c r="F216" t="n">
+      <c r="G216" t="n">
         <v>1359</v>
-      </c>
-      <c r="G216" t="n">
-        <v>3837</v>
       </c>
     </row>
     <row r="217">
@@ -13083,19 +13283,19 @@
         <v>7002</v>
       </c>
       <c r="C217" t="n">
+        <v>4094</v>
+      </c>
+      <c r="D217" t="n">
         <v>3061</v>
       </c>
-      <c r="D217" t="n">
+      <c r="E217" t="n">
         <v>2830</v>
       </c>
-      <c r="E217" t="n">
+      <c r="F217" t="n">
         <v>3704</v>
       </c>
-      <c r="F217" t="n">
+      <c r="G217" t="n">
         <v>1359</v>
-      </c>
-      <c r="G217" t="n">
-        <v>4094</v>
       </c>
     </row>
     <row r="218">
@@ -13108,19 +13308,19 @@
         <v>7002</v>
       </c>
       <c r="C218" t="n">
+        <v>4132</v>
+      </c>
+      <c r="D218" t="n">
         <v>3022</v>
       </c>
-      <c r="D218" t="n">
+      <c r="E218" t="n">
         <v>2969</v>
       </c>
-      <c r="E218" t="n">
+      <c r="F218" t="n">
         <v>3704</v>
       </c>
-      <c r="F218" t="n">
+      <c r="G218" t="n">
         <v>1359</v>
-      </c>
-      <c r="G218" t="n">
-        <v>4132</v>
       </c>
     </row>
     <row r="219">
@@ -13133,19 +13333,19 @@
         <v>7045</v>
       </c>
       <c r="C219" t="n">
+        <v>4165</v>
+      </c>
+      <c r="D219" t="n">
         <v>3133</v>
       </c>
-      <c r="D219" t="n">
+      <c r="E219" t="n">
         <v>2992</v>
       </c>
-      <c r="E219" t="n">
+      <c r="F219" t="n">
         <v>3758</v>
       </c>
-      <c r="F219" t="n">
+      <c r="G219" t="n">
         <v>1345</v>
-      </c>
-      <c r="G219" t="n">
-        <v>4165</v>
       </c>
     </row>
     <row r="220">
@@ -13158,19 +13358,19 @@
         <v>7109</v>
       </c>
       <c r="C220" t="n">
+        <v>4151</v>
+      </c>
+      <c r="D220" t="n">
         <v>3096</v>
       </c>
-      <c r="D220" t="n">
+      <c r="E220" t="n">
         <v>3171</v>
       </c>
-      <c r="E220" t="n">
+      <c r="F220" t="n">
         <v>3886</v>
       </c>
-      <c r="F220" t="n">
+      <c r="G220" t="n">
         <v>1359</v>
-      </c>
-      <c r="G220" t="n">
-        <v>4151</v>
       </c>
     </row>
     <row r="221">
@@ -13183,19 +13383,19 @@
         <v>7109</v>
       </c>
       <c r="C221" t="n">
+        <v>4175</v>
+      </c>
+      <c r="D221" t="n">
         <v>3096</v>
       </c>
-      <c r="D221" t="n">
+      <c r="E221" t="n">
         <v>3246</v>
       </c>
-      <c r="E221" t="n">
+      <c r="F221" t="n">
         <v>3938</v>
       </c>
-      <c r="F221" t="n">
+      <c r="G221" t="n">
         <v>1359</v>
-      </c>
-      <c r="G221" t="n">
-        <v>4175</v>
       </c>
     </row>
     <row r="222">
@@ -13208,19 +13408,19 @@
         <v>7109</v>
       </c>
       <c r="C222" t="n">
+        <v>4271</v>
+      </c>
+      <c r="D222" t="n">
         <v>3186</v>
       </c>
-      <c r="D222" t="n">
+      <c r="E222" t="n">
         <v>3324</v>
       </c>
-      <c r="E222" t="n">
+      <c r="F222" t="n">
         <v>4171</v>
       </c>
-      <c r="F222" t="n">
+      <c r="G222" t="n">
         <v>1359</v>
-      </c>
-      <c r="G222" t="n">
-        <v>4271</v>
       </c>
     </row>
     <row r="223">
@@ -13233,19 +13433,19 @@
         <v>7109</v>
       </c>
       <c r="C223" t="n">
+        <v>4432</v>
+      </c>
+      <c r="D223" t="n">
         <v>3210</v>
       </c>
-      <c r="D223" t="n">
+      <c r="E223" t="n">
         <v>3613</v>
       </c>
-      <c r="E223" t="n">
+      <c r="F223" t="n">
         <v>4444</v>
       </c>
-      <c r="F223" t="n">
+      <c r="G223" t="n">
         <v>1359</v>
-      </c>
-      <c r="G223" t="n">
-        <v>4432</v>
       </c>
     </row>
     <row r="224">
@@ -13258,19 +13458,19 @@
         <v>7109</v>
       </c>
       <c r="C224" t="n">
+        <v>4531</v>
+      </c>
+      <c r="D224" t="n">
         <v>3293</v>
       </c>
-      <c r="D224" t="n">
+      <c r="E224" t="n">
         <v>3936</v>
       </c>
-      <c r="E224" t="n">
+      <c r="F224" t="n">
         <v>4570</v>
       </c>
-      <c r="F224" t="n">
+      <c r="G224" t="n">
         <v>1359</v>
-      </c>
-      <c r="G224" t="n">
-        <v>4531</v>
       </c>
     </row>
     <row r="225">
@@ -13283,19 +13483,19 @@
         <v>7092</v>
       </c>
       <c r="C225" t="n">
+        <v>4720</v>
+      </c>
+      <c r="D225" t="n">
         <v>3293</v>
       </c>
-      <c r="D225" t="n">
+      <c r="E225" t="n">
         <v>4080</v>
       </c>
-      <c r="E225" t="n">
+      <c r="F225" t="n">
         <v>4820</v>
       </c>
-      <c r="F225" t="n">
+      <c r="G225" t="n">
         <v>1383</v>
-      </c>
-      <c r="G225" t="n">
-        <v>4720</v>
       </c>
     </row>
     <row r="226">
@@ -13308,19 +13508,19 @@
         <v>7183</v>
       </c>
       <c r="C226" t="n">
+        <v>4757</v>
+      </c>
+      <c r="D226" t="n">
         <v>3616</v>
       </c>
-      <c r="D226" t="n">
+      <c r="E226" t="n">
         <v>4035</v>
       </c>
-      <c r="E226" t="n">
+      <c r="F226" t="n">
         <v>4794</v>
       </c>
-      <c r="F226" t="n">
+      <c r="G226" t="n">
         <v>1446</v>
-      </c>
-      <c r="G226" t="n">
-        <v>4757</v>
       </c>
     </row>
     <row r="227">
@@ -13333,19 +13533,19 @@
         <v>7183</v>
       </c>
       <c r="C227" t="n">
+        <v>4691</v>
+      </c>
+      <c r="D227" t="n">
         <v>4391</v>
       </c>
-      <c r="D227" t="n">
+      <c r="E227" t="n">
         <v>4003</v>
       </c>
-      <c r="E227" t="n">
+      <c r="F227" t="n">
         <v>4845</v>
       </c>
-      <c r="F227" t="n">
+      <c r="G227" t="n">
         <v>1504</v>
-      </c>
-      <c r="G227" t="n">
-        <v>4691</v>
       </c>
     </row>
     <row r="228">
@@ -13358,19 +13558,19 @@
         <v>7183</v>
       </c>
       <c r="C228" t="n">
+        <v>4626</v>
+      </c>
+      <c r="D228" t="n">
         <v>4619</v>
       </c>
-      <c r="D228" t="n">
+      <c r="E228" t="n">
         <v>3971</v>
       </c>
-      <c r="E228" t="n">
+      <c r="F228" t="n">
         <v>4746</v>
       </c>
-      <c r="F228" t="n">
+      <c r="G228" t="n">
         <v>1526</v>
-      </c>
-      <c r="G228" t="n">
-        <v>4626</v>
       </c>
     </row>
     <row r="229">
@@ -13383,19 +13583,19 @@
         <v>7183</v>
       </c>
       <c r="C229" t="n">
+        <v>4498</v>
+      </c>
+      <c r="D229" t="n">
         <v>4512</v>
       </c>
-      <c r="D229" t="n">
+      <c r="E229" t="n">
         <v>3811</v>
       </c>
-      <c r="E229" t="n">
+      <c r="F229" t="n">
         <v>4688</v>
       </c>
-      <c r="F229" t="n">
+      <c r="G229" t="n">
         <v>1632</v>
-      </c>
-      <c r="G229" t="n">
-        <v>4498</v>
       </c>
     </row>
     <row r="230">
@@ -13408,19 +13608,19 @@
         <v>7363</v>
       </c>
       <c r="C230" t="n">
+        <v>4474</v>
+      </c>
+      <c r="D230" t="n">
         <v>4426</v>
       </c>
-      <c r="D230" t="n">
+      <c r="E230" t="n">
         <v>3811</v>
       </c>
-      <c r="E230" t="n">
+      <c r="F230" t="n">
         <v>4402</v>
       </c>
-      <c r="F230" t="n">
+      <c r="G230" t="n">
         <v>1632</v>
-      </c>
-      <c r="G230" t="n">
-        <v>4474</v>
       </c>
     </row>
     <row r="231">
@@ -13433,19 +13633,19 @@
         <v>7130</v>
       </c>
       <c r="C231" t="n">
+        <v>4412</v>
+      </c>
+      <c r="D231" t="n">
         <v>4446</v>
       </c>
-      <c r="D231" t="n">
+      <c r="E231" t="n">
         <v>3876</v>
       </c>
-      <c r="E231" t="n">
+      <c r="F231" t="n">
         <v>4402</v>
       </c>
-      <c r="F231" t="n">
+      <c r="G231" t="n">
         <v>1632</v>
-      </c>
-      <c r="G231" t="n">
-        <v>4412</v>
       </c>
     </row>
     <row r="232">
@@ -13458,19 +13658,19 @@
         <v>7363</v>
       </c>
       <c r="C232" t="n">
+        <v>4401</v>
+      </c>
+      <c r="D232" t="n">
         <v>4172</v>
       </c>
-      <c r="D232" t="n">
+      <c r="E232" t="n">
         <v>3876</v>
       </c>
-      <c r="E232" t="n">
+      <c r="F232" t="n">
         <v>4206</v>
       </c>
-      <c r="F232" t="n">
+      <c r="G232" t="n">
         <v>1669</v>
-      </c>
-      <c r="G232" t="n">
-        <v>4401</v>
       </c>
     </row>
     <row r="233">
@@ -13483,19 +13683,19 @@
         <v>7363</v>
       </c>
       <c r="C233" t="n">
+        <v>4477</v>
+      </c>
+      <c r="D233" t="n">
         <v>4172</v>
       </c>
-      <c r="D233" t="n">
+      <c r="E233" t="n">
         <v>3899</v>
       </c>
-      <c r="E233" t="n">
+      <c r="F233" t="n">
         <v>4178</v>
       </c>
-      <c r="F233" t="n">
+      <c r="G233" t="n">
         <v>2385</v>
-      </c>
-      <c r="G233" t="n">
-        <v>4477</v>
       </c>
     </row>
     <row r="234">
@@ -13508,19 +13708,19 @@
         <v>7363</v>
       </c>
       <c r="C234" t="n">
+        <v>4446</v>
+      </c>
+      <c r="D234" t="n">
         <v>4072</v>
       </c>
-      <c r="D234" t="n">
+      <c r="E234" t="n">
         <v>3913</v>
       </c>
-      <c r="E234" t="n">
+      <c r="F234" t="n">
         <v>4602</v>
       </c>
-      <c r="F234" t="n">
+      <c r="G234" t="n">
         <v>3722</v>
-      </c>
-      <c r="G234" t="n">
-        <v>4446</v>
       </c>
     </row>
     <row r="235">
@@ -13533,19 +13733,19 @@
         <v>7363</v>
       </c>
       <c r="C235" t="n">
+        <v>4438</v>
+      </c>
+      <c r="D235" t="n">
         <v>4047</v>
       </c>
-      <c r="D235" t="n">
+      <c r="E235" t="n">
         <v>4022</v>
       </c>
-      <c r="E235" t="n">
+      <c r="F235" t="n">
         <v>4587</v>
       </c>
-      <c r="F235" t="n">
+      <c r="G235" t="n">
         <v>3431</v>
-      </c>
-      <c r="G235" t="n">
-        <v>4438</v>
       </c>
     </row>
     <row r="236">
@@ -13558,19 +13758,19 @@
         <v>7363</v>
       </c>
       <c r="C236" t="n">
+        <v>4342</v>
+      </c>
+      <c r="D236" t="n">
         <v>3929</v>
       </c>
-      <c r="D236" t="n">
+      <c r="E236" t="n">
         <v>3688</v>
       </c>
-      <c r="E236" t="n">
+      <c r="F236" t="n">
         <v>4266</v>
       </c>
-      <c r="F236" t="n">
+      <c r="G236" t="n">
         <v>3079</v>
-      </c>
-      <c r="G236" t="n">
-        <v>4342</v>
       </c>
     </row>
     <row r="237">
@@ -13583,19 +13783,19 @@
         <v>7363</v>
       </c>
       <c r="C237" t="n">
+        <v>3935</v>
+      </c>
+      <c r="D237" t="n">
         <v>3831</v>
       </c>
-      <c r="D237" t="n">
+      <c r="E237" t="n">
         <v>3655</v>
       </c>
-      <c r="E237" t="n">
+      <c r="F237" t="n">
         <v>4216</v>
       </c>
-      <c r="F237" t="n">
+      <c r="G237" t="n">
         <v>2843</v>
-      </c>
-      <c r="G237" t="n">
-        <v>3935</v>
       </c>
     </row>
     <row r="238">
@@ -13608,19 +13808,19 @@
         <v>7363</v>
       </c>
       <c r="C238" t="n">
+        <v>3833</v>
+      </c>
+      <c r="D238" t="n">
         <v>3732</v>
       </c>
-      <c r="D238" t="n">
+      <c r="E238" t="n">
         <v>3466</v>
       </c>
-      <c r="E238" t="n">
+      <c r="F238" t="n">
         <v>4361</v>
       </c>
-      <c r="F238" t="n">
+      <c r="G238" t="n">
         <v>2675</v>
-      </c>
-      <c r="G238" t="n">
-        <v>3833</v>
       </c>
     </row>
     <row r="239">
@@ -13633,19 +13833,19 @@
         <v>7429</v>
       </c>
       <c r="C239" t="n">
+        <v>3768</v>
+      </c>
+      <c r="D239" t="n">
         <v>3636</v>
       </c>
-      <c r="D239" t="n">
+      <c r="E239" t="n">
         <v>3389</v>
       </c>
-      <c r="E239" t="n">
+      <c r="F239" t="n">
         <v>4264</v>
       </c>
-      <c r="F239" t="n">
+      <c r="G239" t="n">
         <v>2555</v>
-      </c>
-      <c r="G239" t="n">
-        <v>3768</v>
       </c>
     </row>
     <row r="240">
@@ -13658,19 +13858,19 @@
         <v>7676</v>
       </c>
       <c r="C240" t="n">
+        <v>3760</v>
+      </c>
+      <c r="D240" t="n">
         <v>3581</v>
       </c>
-      <c r="D240" t="n">
+      <c r="E240" t="n">
         <v>3345</v>
       </c>
-      <c r="E240" t="n">
+      <c r="F240" t="n">
         <v>3942</v>
       </c>
-      <c r="F240" t="n">
+      <c r="G240" t="n">
         <v>2478</v>
-      </c>
-      <c r="G240" t="n">
-        <v>3760</v>
       </c>
     </row>
     <row r="241">
@@ -13683,19 +13883,19 @@
         <v>7432</v>
       </c>
       <c r="C241" t="n">
+        <v>3661</v>
+      </c>
+      <c r="D241" t="n">
         <v>3582</v>
       </c>
-      <c r="D241" t="n">
+      <c r="E241" t="n">
         <v>3342</v>
       </c>
-      <c r="E241" t="n">
+      <c r="F241" t="n">
         <v>3856</v>
       </c>
-      <c r="F241" t="n">
+      <c r="G241" t="n">
         <v>2478</v>
-      </c>
-      <c r="G241" t="n">
-        <v>3661</v>
       </c>
     </row>
     <row r="242">
@@ -13708,19 +13908,19 @@
         <v>8050</v>
       </c>
       <c r="C242" t="n">
+        <v>3586</v>
+      </c>
+      <c r="D242" t="n">
         <v>3390</v>
       </c>
-      <c r="D242" t="n">
+      <c r="E242" t="n">
         <v>2934</v>
       </c>
-      <c r="E242" t="n">
+      <c r="F242" t="n">
         <v>3856</v>
       </c>
-      <c r="F242" t="n">
+      <c r="G242" t="n">
         <v>2233</v>
-      </c>
-      <c r="G242" t="n">
-        <v>3586</v>
       </c>
     </row>
     <row r="243">
@@ -13733,19 +13933,19 @@
         <v>8108</v>
       </c>
       <c r="C243" t="n">
+        <v>3512</v>
+      </c>
+      <c r="D243" t="n">
         <v>3495</v>
       </c>
-      <c r="D243" t="n">
+      <c r="E243" t="n">
         <v>2893</v>
       </c>
-      <c r="E243" t="n">
+      <c r="F243" t="n">
         <v>3935</v>
       </c>
-      <c r="F243" t="n">
+      <c r="G243" t="n">
         <v>2216</v>
-      </c>
-      <c r="G243" t="n">
-        <v>3512</v>
       </c>
     </row>
     <row r="244">
@@ -13758,19 +13958,19 @@
         <v>8264</v>
       </c>
       <c r="C244" t="n">
+        <v>3410</v>
+      </c>
+      <c r="D244" t="n">
         <v>3705</v>
       </c>
-      <c r="D244" t="n">
+      <c r="E244" t="n">
         <v>2926</v>
       </c>
-      <c r="E244" t="n">
+      <c r="F244" t="n">
         <v>3819</v>
       </c>
-      <c r="F244" t="n">
+      <c r="G244" t="n">
         <v>2295</v>
-      </c>
-      <c r="G244" t="n">
-        <v>3410</v>
       </c>
     </row>
     <row r="245">
@@ -13783,19 +13983,19 @@
         <v>8264</v>
       </c>
       <c r="C245" t="n">
+        <v>3393</v>
+      </c>
+      <c r="D245" t="n">
         <v>3654</v>
       </c>
-      <c r="D245" t="n">
+      <c r="E245" t="n">
         <v>3004</v>
       </c>
-      <c r="E245" t="n">
+      <c r="F245" t="n">
         <v>3819</v>
       </c>
-      <c r="F245" t="n">
+      <c r="G245" t="n">
         <v>2518</v>
-      </c>
-      <c r="G245" t="n">
-        <v>3393</v>
       </c>
     </row>
     <row r="246">
@@ -13808,19 +14008,19 @@
         <v>8264</v>
       </c>
       <c r="C246" t="n">
+        <v>3387</v>
+      </c>
+      <c r="D246" t="n">
         <v>3605</v>
       </c>
-      <c r="D246" t="n">
+      <c r="E246" t="n">
         <v>3011</v>
       </c>
-      <c r="E246" t="n">
+      <c r="F246" t="n">
         <v>3819</v>
       </c>
-      <c r="F246" t="n">
+      <c r="G246" t="n">
         <v>2518</v>
-      </c>
-      <c r="G246" t="n">
-        <v>3387</v>
       </c>
     </row>
     <row r="247">
@@ -13833,19 +14033,19 @@
         <v>8185</v>
       </c>
       <c r="C247" t="n">
+        <v>3387</v>
+      </c>
+      <c r="D247" t="n">
         <v>3547</v>
       </c>
-      <c r="D247" t="n">
+      <c r="E247" t="n">
         <v>2962</v>
       </c>
-      <c r="E247" t="n">
+      <c r="F247" t="n">
         <v>3819</v>
       </c>
-      <c r="F247" t="n">
+      <c r="G247" t="n">
         <v>2462</v>
-      </c>
-      <c r="G247" t="n">
-        <v>3387</v>
       </c>
     </row>
     <row r="248">
@@ -13858,19 +14058,19 @@
         <v>8185</v>
       </c>
       <c r="C248" t="n">
+        <v>3516</v>
+      </c>
+      <c r="D248" t="n">
         <v>3670</v>
       </c>
-      <c r="D248" t="n">
+      <c r="E248" t="n">
         <v>2866</v>
       </c>
-      <c r="E248" t="n">
+      <c r="F248" t="n">
         <v>4068</v>
       </c>
-      <c r="F248" t="n">
+      <c r="G248" t="n">
         <v>2364</v>
-      </c>
-      <c r="G248" t="n">
-        <v>3516</v>
       </c>
     </row>
     <row r="249">
@@ -13883,19 +14083,19 @@
         <v>8185</v>
       </c>
       <c r="C249" t="n">
+        <v>3531</v>
+      </c>
+      <c r="D249" t="n">
         <v>3526</v>
       </c>
-      <c r="D249" t="n">
+      <c r="E249" t="n">
         <v>2903</v>
       </c>
-      <c r="E249" t="n">
+      <c r="F249" t="n">
         <v>4027</v>
       </c>
-      <c r="F249" t="n">
+      <c r="G249" t="n">
         <v>2468</v>
-      </c>
-      <c r="G249" t="n">
-        <v>3531</v>
       </c>
     </row>
     <row r="250">
@@ -13908,19 +14108,19 @@
         <v>8185</v>
       </c>
       <c r="C250" t="n">
+        <v>3401</v>
+      </c>
+      <c r="D250" t="n">
         <v>3526</v>
       </c>
-      <c r="D250" t="n">
+      <c r="E250" t="n">
         <v>2867</v>
       </c>
-      <c r="E250" t="n">
+      <c r="F250" t="n">
         <v>3845</v>
       </c>
-      <c r="F250" t="n">
+      <c r="G250" t="n">
         <v>2513</v>
-      </c>
-      <c r="G250" t="n">
-        <v>3401</v>
       </c>
     </row>
     <row r="251">
@@ -13933,19 +14133,19 @@
         <v>8185</v>
       </c>
       <c r="C251" t="n">
+        <v>3386</v>
+      </c>
+      <c r="D251" t="n">
         <v>3591</v>
       </c>
-      <c r="D251" t="n">
+      <c r="E251" t="n">
         <v>2867</v>
       </c>
-      <c r="E251" t="n">
+      <c r="F251" t="n">
         <v>3789</v>
       </c>
-      <c r="F251" t="n">
+      <c r="G251" t="n">
         <v>2623</v>
-      </c>
-      <c r="G251" t="n">
-        <v>3386</v>
       </c>
     </row>
     <row r="252">
@@ -13958,19 +14158,19 @@
         <v>8073</v>
       </c>
       <c r="C252" t="n">
+        <v>3439</v>
+      </c>
+      <c r="D252" t="n">
         <v>3629</v>
       </c>
-      <c r="D252" t="n">
+      <c r="E252" t="n">
         <v>2988</v>
       </c>
-      <c r="E252" t="n">
+      <c r="F252" t="n">
         <v>4090</v>
       </c>
-      <c r="F252" t="n">
+      <c r="G252" t="n">
         <v>2761</v>
-      </c>
-      <c r="G252" t="n">
-        <v>3439</v>
       </c>
     </row>
     <row r="253">
@@ -13983,19 +14183,19 @@
         <v>8073</v>
       </c>
       <c r="C253" t="n">
+        <v>3477</v>
+      </c>
+      <c r="D253" t="n">
         <v>3611</v>
       </c>
-      <c r="D253" t="n">
+      <c r="E253" t="n">
         <v>3012</v>
       </c>
-      <c r="E253" t="n">
+      <c r="F253" t="n">
         <v>4151</v>
       </c>
-      <c r="F253" t="n">
+      <c r="G253" t="n">
         <v>2812</v>
-      </c>
-      <c r="G253" t="n">
-        <v>3477</v>
       </c>
     </row>
     <row r="254">
@@ -14008,19 +14208,19 @@
         <v>8073</v>
       </c>
       <c r="C254" t="n">
+        <v>3614</v>
+      </c>
+      <c r="D254" t="n">
         <v>3611</v>
       </c>
-      <c r="D254" t="n">
+      <c r="E254" t="n">
         <v>2970</v>
       </c>
-      <c r="E254" t="n">
+      <c r="F254" t="n">
         <v>4266</v>
       </c>
-      <c r="F254" t="n">
+      <c r="G254" t="n">
         <v>2812</v>
-      </c>
-      <c r="G254" t="n">
-        <v>3614</v>
       </c>
     </row>
     <row r="255">
@@ -14033,19 +14233,19 @@
         <v>7955</v>
       </c>
       <c r="C255" t="n">
+        <v>3682</v>
+      </c>
+      <c r="D255" t="n">
         <v>3659</v>
       </c>
-      <c r="D255" t="n">
+      <c r="E255" t="n">
         <v>2999</v>
       </c>
-      <c r="E255" t="n">
+      <c r="F255" t="n">
         <v>4266</v>
       </c>
-      <c r="F255" t="n">
+      <c r="G255" t="n">
         <v>2812</v>
-      </c>
-      <c r="G255" t="n">
-        <v>3682</v>
       </c>
     </row>
     <row r="256">
@@ -14058,19 +14258,19 @@
         <v>7934</v>
       </c>
       <c r="C256" t="n">
+        <v>3718</v>
+      </c>
+      <c r="D256" t="n">
         <v>3735</v>
       </c>
-      <c r="D256" t="n">
+      <c r="E256" t="n">
         <v>2999</v>
       </c>
-      <c r="E256" t="n">
+      <c r="F256" t="n">
         <v>4266</v>
       </c>
-      <c r="F256" t="n">
+      <c r="G256" t="n">
         <v>2812</v>
-      </c>
-      <c r="G256" t="n">
-        <v>3718</v>
       </c>
     </row>
     <row r="257">
@@ -14083,19 +14283,19 @@
         <v>8031</v>
       </c>
       <c r="C257" t="n">
+        <v>3718</v>
+      </c>
+      <c r="D257" t="n">
         <v>3685</v>
       </c>
-      <c r="D257" t="n">
+      <c r="E257" t="n">
         <v>2999</v>
       </c>
-      <c r="E257" t="n">
+      <c r="F257" t="n">
         <v>4329</v>
       </c>
-      <c r="F257" t="n">
+      <c r="G257" t="n">
         <v>2812</v>
-      </c>
-      <c r="G257" t="n">
-        <v>3718</v>
       </c>
     </row>
     <row r="258">
@@ -14108,19 +14308,19 @@
         <v>8399</v>
       </c>
       <c r="C258" t="n">
+        <v>3677</v>
+      </c>
+      <c r="D258" t="n">
         <v>3636</v>
       </c>
-      <c r="D258" t="n">
+      <c r="E258" t="n">
         <v>2999</v>
       </c>
-      <c r="E258" t="n">
+      <c r="F258" t="n">
         <v>4329</v>
       </c>
-      <c r="F258" t="n">
+      <c r="G258" t="n">
         <v>2812</v>
-      </c>
-      <c r="G258" t="n">
-        <v>3677</v>
       </c>
     </row>
     <row r="259">
@@ -14133,19 +14333,19 @@
         <v>8437</v>
       </c>
       <c r="C259" t="n">
+        <v>3645</v>
+      </c>
+      <c r="D259" t="n">
         <v>3636</v>
       </c>
-      <c r="D259" t="n">
+      <c r="E259" t="n">
         <v>2999</v>
       </c>
-      <c r="E259" t="n">
+      <c r="F259" t="n">
         <v>4329</v>
       </c>
-      <c r="F259" t="n">
+      <c r="G259" t="n">
         <v>2812</v>
-      </c>
-      <c r="G259" t="n">
-        <v>3645</v>
       </c>
     </row>
     <row r="260">
@@ -14158,19 +14358,19 @@
         <v>8394</v>
       </c>
       <c r="C260" t="n">
+        <v>3645</v>
+      </c>
+      <c r="D260" t="n">
         <v>3658</v>
       </c>
-      <c r="D260" t="n">
+      <c r="E260" t="n">
         <v>3035</v>
       </c>
-      <c r="E260" t="n">
+      <c r="F260" t="n">
         <v>4329</v>
       </c>
-      <c r="F260" t="n">
+      <c r="G260" t="n">
         <v>2812</v>
-      </c>
-      <c r="G260" t="n">
-        <v>3645</v>
       </c>
     </row>
     <row r="261">
@@ -14183,19 +14383,19 @@
         <v>8394</v>
       </c>
       <c r="C261" t="n">
+        <v>3827</v>
+      </c>
+      <c r="D261" t="n">
         <v>3578</v>
       </c>
-      <c r="D261" t="n">
+      <c r="E261" t="n">
         <v>3035</v>
       </c>
-      <c r="E261" t="n">
+      <c r="F261" t="n">
         <v>4329</v>
       </c>
-      <c r="F261" t="n">
+      <c r="G261" t="n">
         <v>2812</v>
-      </c>
-      <c r="G261" t="n">
-        <v>3827</v>
       </c>
     </row>
     <row r="262">
@@ -14208,19 +14408,19 @@
         <v>8394</v>
       </c>
       <c r="C262" t="n">
+        <v>3860</v>
+      </c>
+      <c r="D262" t="n">
         <v>3578</v>
       </c>
-      <c r="D262" t="n">
+      <c r="E262" t="n">
         <v>3035</v>
       </c>
-      <c r="E262" t="n">
+      <c r="F262" t="n">
         <v>4329</v>
       </c>
-      <c r="F262" t="n">
+      <c r="G262" t="n">
         <v>2812</v>
-      </c>
-      <c r="G262" t="n">
-        <v>3860</v>
       </c>
     </row>
     <row r="263">
@@ -14233,19 +14433,19 @@
         <v>8437</v>
       </c>
       <c r="C263" t="n">
+        <v>3723</v>
+      </c>
+      <c r="D263" t="n">
         <v>3578</v>
       </c>
-      <c r="D263" t="n">
+      <c r="E263" t="n">
         <v>3035</v>
       </c>
-      <c r="E263" t="n">
+      <c r="F263" t="n">
         <v>4329</v>
       </c>
-      <c r="F263" t="n">
+      <c r="G263" t="n">
         <v>2865</v>
-      </c>
-      <c r="G263" t="n">
-        <v>3723</v>
       </c>
     </row>
     <row r="264">
@@ -14258,19 +14458,19 @@
         <v>8437</v>
       </c>
       <c r="C264" t="n">
+        <v>3723</v>
+      </c>
+      <c r="D264" t="n">
         <v>3636</v>
       </c>
-      <c r="D264" t="n">
+      <c r="E264" t="n">
         <v>3035</v>
       </c>
-      <c r="E264" t="n">
+      <c r="F264" t="n">
         <v>4329</v>
       </c>
-      <c r="F264" t="n">
+      <c r="G264" t="n">
         <v>3005</v>
-      </c>
-      <c r="G264" t="n">
-        <v>3723</v>
       </c>
     </row>
     <row r="265">
@@ -14283,19 +14483,19 @@
         <v>8437</v>
       </c>
       <c r="C265" t="n">
+        <v>3793</v>
+      </c>
+      <c r="D265" t="n">
         <v>3693</v>
       </c>
-      <c r="D265" t="n">
+      <c r="E265" t="n">
         <v>3035</v>
       </c>
-      <c r="E265" t="n">
+      <c r="F265" t="n">
         <v>4329</v>
       </c>
-      <c r="F265" t="n">
+      <c r="G265" t="n">
         <v>3060</v>
-      </c>
-      <c r="G265" t="n">
-        <v>3793</v>
       </c>
     </row>
     <row r="266">
@@ -14308,19 +14508,19 @@
         <v>8398</v>
       </c>
       <c r="C266" t="n">
+        <v>3836</v>
+      </c>
+      <c r="D266" t="n">
         <v>3743</v>
       </c>
-      <c r="D266" t="n">
+      <c r="E266" t="n">
         <v>3035</v>
       </c>
-      <c r="E266" t="n">
+      <c r="F266" t="n">
         <v>4329</v>
       </c>
-      <c r="F266" t="n">
+      <c r="G266" t="n">
         <v>3060</v>
-      </c>
-      <c r="G266" t="n">
-        <v>3836</v>
       </c>
     </row>
     <row r="267">
@@ -14333,19 +14533,19 @@
         <v>8398</v>
       </c>
       <c r="C267" t="n">
+        <v>3836</v>
+      </c>
+      <c r="D267" t="n">
         <v>3743</v>
       </c>
-      <c r="D267" t="n">
+      <c r="E267" t="n">
         <v>3035</v>
       </c>
-      <c r="E267" t="n">
+      <c r="F267" t="n">
         <v>4329</v>
       </c>
-      <c r="F267" t="n">
+      <c r="G267" t="n">
         <v>3156</v>
-      </c>
-      <c r="G267" t="n">
-        <v>3836</v>
       </c>
     </row>
     <row r="268">
@@ -14358,19 +14558,19 @@
         <v>8355</v>
       </c>
       <c r="C268" t="n">
+        <v>3765</v>
+      </c>
+      <c r="D268" t="n">
         <v>3539</v>
       </c>
-      <c r="D268" t="n">
+      <c r="E268" t="n">
         <v>3035</v>
       </c>
-      <c r="E268" t="n">
+      <c r="F268" t="n">
         <v>4329</v>
       </c>
-      <c r="F268" t="n">
+      <c r="G268" t="n">
         <v>3156</v>
-      </c>
-      <c r="G268" t="n">
-        <v>3765</v>
       </c>
     </row>
     <row r="269">
@@ -14383,19 +14583,19 @@
         <v>8355</v>
       </c>
       <c r="C269" t="n">
+        <v>4001</v>
+      </c>
+      <c r="D269" t="n">
         <v>3581</v>
       </c>
-      <c r="D269" t="n">
+      <c r="E269" t="n">
         <v>2999</v>
       </c>
-      <c r="E269" t="n">
+      <c r="F269" t="n">
         <v>4329</v>
       </c>
-      <c r="F269" t="n">
+      <c r="G269" t="n">
         <v>3156</v>
-      </c>
-      <c r="G269" t="n">
-        <v>4001</v>
       </c>
     </row>
     <row r="270">
@@ -14408,19 +14608,19 @@
         <v>8355</v>
       </c>
       <c r="C270" t="n">
+        <v>4001</v>
+      </c>
+      <c r="D270" t="n">
         <v>3672</v>
       </c>
-      <c r="D270" t="n">
+      <c r="E270" t="n">
         <v>3035</v>
       </c>
-      <c r="E270" t="n">
+      <c r="F270" t="n">
         <v>4329</v>
       </c>
-      <c r="F270" t="n">
+      <c r="G270" t="n">
         <v>3156</v>
-      </c>
-      <c r="G270" t="n">
-        <v>4001</v>
       </c>
     </row>
     <row r="271">
@@ -14433,19 +14633,19 @@
         <v>8355</v>
       </c>
       <c r="C271" t="n">
+        <v>4001</v>
+      </c>
+      <c r="D271" t="n">
         <v>3795</v>
       </c>
-      <c r="D271" t="n">
+      <c r="E271" t="n">
         <v>3035</v>
       </c>
-      <c r="E271" t="n">
+      <c r="F271" t="n">
         <v>4329</v>
       </c>
-      <c r="F271" t="n">
+      <c r="G271" t="n">
         <v>3156</v>
-      </c>
-      <c r="G271" t="n">
-        <v>4001</v>
       </c>
     </row>
     <row r="272">
@@ -14458,19 +14658,19 @@
         <v>8355</v>
       </c>
       <c r="C272" t="n">
+        <v>3985</v>
+      </c>
+      <c r="D272" t="n">
         <v>3795</v>
       </c>
-      <c r="D272" t="n">
+      <c r="E272" t="n">
         <v>3035</v>
       </c>
-      <c r="E272" t="n">
+      <c r="F272" t="n">
         <v>4387</v>
       </c>
-      <c r="F272" t="n">
+      <c r="G272" t="n">
         <v>3156</v>
-      </c>
-      <c r="G272" t="n">
-        <v>3985</v>
       </c>
     </row>
     <row r="273">
@@ -14483,19 +14683,19 @@
         <v>8457</v>
       </c>
       <c r="C273" t="n">
+        <v>4165</v>
+      </c>
+      <c r="D273" t="n">
         <v>3840</v>
       </c>
-      <c r="D273" t="n">
+      <c r="E273" t="n">
         <v>3049</v>
       </c>
-      <c r="E273" t="n">
+      <c r="F273" t="n">
         <v>4445</v>
       </c>
-      <c r="F273" t="n">
+      <c r="G273" t="n">
         <v>3108</v>
-      </c>
-      <c r="G273" t="n">
-        <v>4165</v>
       </c>
     </row>
     <row r="274">
@@ -14508,19 +14708,19 @@
         <v>8366</v>
       </c>
       <c r="C274" t="n">
+        <v>4165</v>
+      </c>
+      <c r="D274" t="n">
         <v>3840</v>
       </c>
-      <c r="D274" t="n">
+      <c r="E274" t="n">
         <v>3079</v>
       </c>
-      <c r="E274" t="n">
+      <c r="F274" t="n">
         <v>4445</v>
       </c>
-      <c r="F274" t="n">
+      <c r="G274" t="n">
         <v>3108</v>
-      </c>
-      <c r="G274" t="n">
-        <v>4165</v>
       </c>
     </row>
     <row r="275">
@@ -14533,19 +14733,19 @@
         <v>8366</v>
       </c>
       <c r="C275" t="n">
+        <v>4165</v>
+      </c>
+      <c r="D275" t="n">
         <v>3821</v>
       </c>
-      <c r="D275" t="n">
+      <c r="E275" t="n">
         <v>3210</v>
       </c>
-      <c r="E275" t="n">
+      <c r="F275" t="n">
         <v>4445</v>
       </c>
-      <c r="F275" t="n">
+      <c r="G275" t="n">
         <v>3108</v>
-      </c>
-      <c r="G275" t="n">
-        <v>4165</v>
       </c>
     </row>
     <row r="276">
@@ -14558,19 +14758,19 @@
         <v>8083</v>
       </c>
       <c r="C276" t="n">
+        <v>4093</v>
+      </c>
+      <c r="D276" t="n">
         <v>3858</v>
       </c>
-      <c r="D276" t="n">
+      <c r="E276" t="n">
         <v>3182</v>
       </c>
-      <c r="E276" t="n">
+      <c r="F276" t="n">
         <v>4285</v>
       </c>
-      <c r="F276" t="n">
+      <c r="G276" t="n">
         <v>3101</v>
-      </c>
-      <c r="G276" t="n">
-        <v>4093</v>
       </c>
     </row>
     <row r="277">
@@ -14583,19 +14783,19 @@
         <v>8083</v>
       </c>
       <c r="C277" t="n">
+        <v>4170</v>
+      </c>
+      <c r="D277" t="n">
         <v>5182</v>
       </c>
-      <c r="D277" t="n">
+      <c r="E277" t="n">
         <v>3241</v>
       </c>
-      <c r="E277" t="n">
+      <c r="F277" t="n">
         <v>4612</v>
       </c>
-      <c r="F277" t="n">
+      <c r="G277" t="n">
         <v>3101</v>
-      </c>
-      <c r="G277" t="n">
-        <v>4170</v>
       </c>
     </row>
     <row r="278">
@@ -14608,19 +14808,19 @@
         <v>8083</v>
       </c>
       <c r="C278" t="n">
+        <v>4206</v>
+      </c>
+      <c r="D278" t="n">
         <v>5182</v>
       </c>
-      <c r="D278" t="n">
+      <c r="E278" t="n">
         <v>3316</v>
       </c>
-      <c r="E278" t="n">
+      <c r="F278" t="n">
         <v>4612</v>
       </c>
-      <c r="F278" t="n">
+      <c r="G278" t="n">
         <v>3515</v>
-      </c>
-      <c r="G278" t="n">
-        <v>4206</v>
       </c>
     </row>
     <row r="279">
@@ -14633,19 +14833,19 @@
         <v>8219</v>
       </c>
       <c r="C279" t="n">
+        <v>4418</v>
+      </c>
+      <c r="D279" t="n">
         <v>4892</v>
       </c>
-      <c r="D279" t="n">
+      <c r="E279" t="n">
         <v>3391</v>
       </c>
-      <c r="E279" t="n">
+      <c r="F279" t="n">
         <v>4612</v>
       </c>
-      <c r="F279" t="n">
+      <c r="G279" t="n">
         <v>3662</v>
-      </c>
-      <c r="G279" t="n">
-        <v>4418</v>
       </c>
     </row>
     <row r="280">
@@ -14658,19 +14858,19 @@
         <v>8219</v>
       </c>
       <c r="C280" t="n">
+        <v>4418</v>
+      </c>
+      <c r="D280" t="n">
         <v>4768</v>
       </c>
-      <c r="D280" t="n">
+      <c r="E280" t="n">
         <v>3436</v>
       </c>
-      <c r="E280" t="n">
+      <c r="F280" t="n">
         <v>4612</v>
       </c>
-      <c r="F280" t="n">
+      <c r="G280" t="n">
         <v>3712</v>
-      </c>
-      <c r="G280" t="n">
-        <v>4418</v>
       </c>
     </row>
     <row r="281">
@@ -14683,19 +14883,19 @@
         <v>8219</v>
       </c>
       <c r="C281" t="n">
+        <v>4415</v>
+      </c>
+      <c r="D281" t="n">
         <v>4887</v>
       </c>
-      <c r="D281" t="n">
+      <c r="E281" t="n">
         <v>3436</v>
       </c>
-      <c r="E281" t="n">
+      <c r="F281" t="n">
         <v>4542</v>
       </c>
-      <c r="F281" t="n">
+      <c r="G281" t="n">
         <v>3735</v>
-      </c>
-      <c r="G281" t="n">
-        <v>4415</v>
       </c>
     </row>
     <row r="282">
@@ -14708,19 +14908,19 @@
         <v>8219</v>
       </c>
       <c r="C282" t="n">
+        <v>4531</v>
+      </c>
+      <c r="D282" t="n">
         <v>4268</v>
       </c>
-      <c r="D282" t="n">
+      <c r="E282" t="n">
         <v>3751</v>
       </c>
-      <c r="E282" t="n">
+      <c r="F282" t="n">
         <v>4657</v>
       </c>
-      <c r="F282" t="n">
+      <c r="G282" t="n">
         <v>4299</v>
-      </c>
-      <c r="G282" t="n">
-        <v>4531</v>
       </c>
     </row>
     <row r="283">
@@ -14733,19 +14933,19 @@
         <v>8219</v>
       </c>
       <c r="C283" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D283" t="n">
         <v>3841</v>
       </c>
-      <c r="D283" t="n">
+      <c r="E283" t="n">
         <v>3872</v>
       </c>
-      <c r="E283" t="n">
+      <c r="F283" t="n">
         <v>4713</v>
       </c>
-      <c r="F283" t="n">
+      <c r="G283" t="n">
         <v>4299</v>
-      </c>
-      <c r="G283" t="n">
-        <v>4773</v>
       </c>
     </row>
     <row r="284">
@@ -14758,19 +14958,19 @@
         <v>8219</v>
       </c>
       <c r="C284" t="n">
+        <v>4810</v>
+      </c>
+      <c r="D284" t="n">
         <v>3706</v>
       </c>
-      <c r="D284" t="n">
+      <c r="E284" t="n">
         <v>3910</v>
       </c>
-      <c r="E284" t="n">
+      <c r="F284" t="n">
         <v>4686</v>
       </c>
-      <c r="F284" t="n">
+      <c r="G284" t="n">
         <v>3523</v>
-      </c>
-      <c r="G284" t="n">
-        <v>4810</v>
       </c>
     </row>
     <row r="285">
@@ -14783,19 +14983,19 @@
         <v>8219</v>
       </c>
       <c r="C285" t="n">
+        <v>4618</v>
+      </c>
+      <c r="D285" t="n">
         <v>3405</v>
       </c>
-      <c r="D285" t="n">
+      <c r="E285" t="n">
         <v>3976</v>
       </c>
-      <c r="E285" t="n">
+      <c r="F285" t="n">
         <v>4523</v>
       </c>
-      <c r="F285" t="n">
+      <c r="G285" t="n">
         <v>2883</v>
-      </c>
-      <c r="G285" t="n">
-        <v>4618</v>
       </c>
     </row>
     <row r="286">
@@ -14808,19 +15008,19 @@
         <v>8219</v>
       </c>
       <c r="C286" t="n">
+        <v>4214</v>
+      </c>
+      <c r="D286" t="n">
         <v>3405</v>
       </c>
-      <c r="D286" t="n">
+      <c r="E286" t="n">
         <v>3818</v>
       </c>
-      <c r="E286" t="n">
+      <c r="F286" t="n">
         <v>4421</v>
       </c>
-      <c r="F286" t="n">
+      <c r="G286" t="n">
         <v>2577</v>
-      </c>
-      <c r="G286" t="n">
-        <v>4214</v>
       </c>
     </row>
     <row r="287">
@@ -14833,19 +15033,19 @@
         <v>8219</v>
       </c>
       <c r="C287" t="n">
+        <v>4055</v>
+      </c>
+      <c r="D287" t="n">
         <v>3321</v>
       </c>
-      <c r="D287" t="n">
+      <c r="E287" t="n">
         <v>3568</v>
       </c>
-      <c r="E287" t="n">
+      <c r="F287" t="n">
         <v>4224</v>
       </c>
-      <c r="F287" t="n">
+      <c r="G287" t="n">
         <v>2403</v>
-      </c>
-      <c r="G287" t="n">
-        <v>4055</v>
       </c>
     </row>
     <row r="288">
@@ -14858,19 +15058,219 @@
         <v>8219</v>
       </c>
       <c r="C288" t="n">
+        <v>3555</v>
+      </c>
+      <c r="D288" t="n">
         <v>2897</v>
       </c>
-      <c r="D288" t="n">
+      <c r="E288" t="n">
         <v>3695</v>
       </c>
-      <c r="E288" t="n">
+      <c r="F288" t="n">
         <v>3954</v>
       </c>
-      <c r="F288" t="n">
+      <c r="G288" t="n">
         <v>2072</v>
       </c>
-      <c r="G288" t="n">
-        <v>3555</v>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3571</v>
+      </c>
+      <c r="D289" t="n">
+        <v>2950</v>
+      </c>
+      <c r="E289" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3954</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3466</v>
+      </c>
+      <c r="D290" t="n">
+        <v>2876</v>
+      </c>
+      <c r="E290" t="n">
+        <v>3552</v>
+      </c>
+      <c r="F290" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2876</v>
+      </c>
+      <c r="E291" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F291" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D292" t="n">
+        <v>2855</v>
+      </c>
+      <c r="E292" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F292" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2855</v>
+      </c>
+      <c r="E293" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F293" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C294" t="n">
+        <v>3015</v>
+      </c>
+      <c r="D294" t="n">
+        <v>2759</v>
+      </c>
+      <c r="E294" t="n">
+        <v>3422</v>
+      </c>
+      <c r="F294" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G294" t="n">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C295" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2759</v>
+      </c>
+      <c r="E295" t="n">
+        <v>3515</v>
+      </c>
+      <c r="F295" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G295" t="n">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D296" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E296" t="n">
+        <v>3618</v>
+      </c>
+      <c r="F296" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G296" t="n">
+        <v>2274</v>
       </c>
     </row>
   </sheetData>
